--- a/LISTA_CLIENTI.xlsx
+++ b/LISTA_CLIENTI.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3844" uniqueCount="841">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3850" uniqueCount="844">
   <si>
     <t>denumire</t>
   </si>
@@ -2537,6 +2537,15 @@
   </si>
   <si>
     <t>J2002000035017</t>
+  </si>
+  <si>
+    <t>DAIANA PIESE SI ACCESORII AUTO SRL</t>
+  </si>
+  <si>
+    <t>J2020000328203</t>
+  </si>
+  <si>
+    <t>STR.EROILOR BL.A SC.E</t>
   </si>
 </sst>
 </file>
@@ -2615,8 +2624,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:T209" totalsRowShown="0">
-  <autoFilter ref="A1:T209"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:T210" totalsRowShown="0">
+  <autoFilter ref="A1:T210"/>
   <tableColumns count="20">
     <tableColumn id="1" name="denumire"/>
     <tableColumn id="2" name="cod_fiscal"/>
@@ -2928,7 +2937,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T209"/>
+  <dimension ref="A1:T210"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="45.85546875" customWidth="1"/>
@@ -15632,6 +15641,42 @@
       <c r="S209" s="2"/>
       <c r="T209" s="2"/>
     </row>
+    <row r="210" spans="1:20" ht="17.25">
+      <c r="A210" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="B210" s="4">
+        <v>42392937</v>
+      </c>
+      <c r="C210" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D210" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E210" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="F210" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="G210" s="2"/>
+      <c r="H210" s="2"/>
+      <c r="I210" s="2"/>
+      <c r="J210" s="2"/>
+      <c r="K210" s="2"/>
+      <c r="L210" s="6" t="s">
+        <v>842</v>
+      </c>
+      <c r="M210" s="2"/>
+      <c r="N210" s="2"/>
+      <c r="O210" s="2"/>
+      <c r="P210" s="2"/>
+      <c r="Q210" s="2"/>
+      <c r="R210" s="2"/>
+      <c r="S210" s="2"/>
+      <c r="T210" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/LISTA_CLIENTI.xlsx
+++ b/LISTA_CLIENTI.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3850" uniqueCount="844">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3856" uniqueCount="848">
   <si>
     <t>denumire</t>
   </si>
@@ -2546,6 +2546,18 @@
   </si>
   <si>
     <t>STR.EROILOR BL.A SC.E</t>
+  </si>
+  <si>
+    <t>ROXEMA TEAM SRL</t>
+  </si>
+  <si>
+    <t>BISTRA</t>
+  </si>
+  <si>
+    <t>CALEA TURZII 25</t>
+  </si>
+  <si>
+    <t>J01/90/2017</t>
   </si>
 </sst>
 </file>
@@ -2599,7 +2611,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
@@ -2614,6 +2626,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2624,8 +2637,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:T210" totalsRowShown="0">
-  <autoFilter ref="A1:T210"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:T211" totalsRowShown="0">
+  <autoFilter ref="A1:T211"/>
   <tableColumns count="20">
     <tableColumn id="1" name="denumire"/>
     <tableColumn id="2" name="cod_fiscal"/>
@@ -2937,7 +2950,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T210"/>
+  <dimension ref="A1:T211"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="45.85546875" customWidth="1"/>
@@ -15677,6 +15690,42 @@
       <c r="S210" s="2"/>
       <c r="T210" s="2"/>
     </row>
+    <row r="211" spans="1:20" ht="17.25">
+      <c r="A211" s="8" t="s">
+        <v>844</v>
+      </c>
+      <c r="B211" s="4">
+        <v>37004621</v>
+      </c>
+      <c r="C211" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D211" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E211" s="2" t="s">
+        <v>845</v>
+      </c>
+      <c r="F211" s="2" t="s">
+        <v>846</v>
+      </c>
+      <c r="G211" s="2"/>
+      <c r="H211" s="2"/>
+      <c r="I211" s="2"/>
+      <c r="J211" s="2"/>
+      <c r="K211" s="2"/>
+      <c r="L211" s="4" t="s">
+        <v>847</v>
+      </c>
+      <c r="M211" s="2"/>
+      <c r="N211" s="2"/>
+      <c r="O211" s="2"/>
+      <c r="P211" s="2"/>
+      <c r="Q211" s="2"/>
+      <c r="R211" s="2"/>
+      <c r="S211" s="2"/>
+      <c r="T211" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/LISTA_CLIENTI.xlsx
+++ b/LISTA_CLIENTI.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3856" uniqueCount="848">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3861" uniqueCount="850">
   <si>
     <t>denumire</t>
   </si>
@@ -2558,6 +2558,12 @@
   </si>
   <si>
     <t>J01/90/2017</t>
+  </si>
+  <si>
+    <t>LAURA IOANA BAURDA - ARHITECT</t>
+  </si>
+  <si>
+    <t>IOAN ALEXANDRU, NR37A, AP15</t>
   </si>
 </sst>
 </file>
@@ -2637,8 +2643,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:T211" totalsRowShown="0">
-  <autoFilter ref="A1:T211"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:T213" totalsRowShown="0">
+  <autoFilter ref="A1:T213"/>
   <tableColumns count="20">
     <tableColumn id="1" name="denumire"/>
     <tableColumn id="2" name="cod_fiscal"/>
@@ -2950,7 +2956,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T211"/>
+  <dimension ref="A1:T213"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="45.85546875" customWidth="1"/>
@@ -15726,6 +15732,62 @@
       <c r="S211" s="2"/>
       <c r="T211" s="2"/>
     </row>
+    <row r="212" spans="1:20">
+      <c r="A212" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="B212" s="2">
+        <v>24338654</v>
+      </c>
+      <c r="C212" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D212" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E212" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F212" s="2" t="s">
+        <v>849</v>
+      </c>
+      <c r="G212" s="2"/>
+      <c r="H212" s="2"/>
+      <c r="I212" s="2"/>
+      <c r="J212" s="2"/>
+      <c r="K212" s="2"/>
+      <c r="L212" s="2"/>
+      <c r="M212" s="2"/>
+      <c r="N212" s="2"/>
+      <c r="O212" s="2"/>
+      <c r="P212" s="2"/>
+      <c r="Q212" s="2"/>
+      <c r="R212" s="2"/>
+      <c r="S212" s="2"/>
+      <c r="T212" s="2"/>
+    </row>
+    <row r="213" spans="1:20">
+      <c r="A213" s="2"/>
+      <c r="B213" s="2"/>
+      <c r="C213" s="2"/>
+      <c r="D213" s="2"/>
+      <c r="E213" s="2"/>
+      <c r="F213" s="2"/>
+      <c r="G213" s="2"/>
+      <c r="H213" s="2"/>
+      <c r="I213" s="2"/>
+      <c r="J213" s="2"/>
+      <c r="K213" s="2"/>
+      <c r="L213" s="2"/>
+      <c r="M213" s="2"/>
+      <c r="N213" s="2"/>
+      <c r="O213" s="2"/>
+      <c r="P213" s="2"/>
+      <c r="Q213" s="2"/>
+      <c r="R213" s="2"/>
+      <c r="S213" s="2"/>
+      <c r="T213" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/LISTA_CLIENTI.xlsx
+++ b/LISTA_CLIENTI.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3861" uniqueCount="850">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3842" uniqueCount="847">
   <si>
     <t>denumire</t>
   </si>
@@ -568,16 +568,7 @@
     <t>J20/112/2013</t>
   </si>
   <si>
-    <t>CCS TEHNIK GARAGE SRL</t>
-  </si>
-  <si>
     <t>RO44945812</t>
-  </si>
-  <si>
-    <t>PRICAZULUI BL.26 SC.A ET.2</t>
-  </si>
-  <si>
-    <t>J2021001443203</t>
   </si>
   <si>
     <t>COLUMBUS SPEDITIONS SRL</t>
@@ -2643,8 +2634,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:T213" totalsRowShown="0">
-  <autoFilter ref="A1:T213"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:T212" totalsRowShown="0">
+  <autoFilter ref="A1:T212"/>
   <tableColumns count="20">
     <tableColumn id="1" name="denumire"/>
     <tableColumn id="2" name="cod_fiscal"/>
@@ -2956,7 +2947,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T213"/>
+  <dimension ref="A1:T212"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="45.85546875" customWidth="1"/>
@@ -3218,7 +3209,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="B5" s="1">
         <v>54286204</v>
@@ -3233,10 +3224,10 @@
         <v>84</v>
       </c>
       <c r="F5" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="L5" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="T5" t="s">
         <v>47</v>
@@ -3740,7 +3731,7 @@
     </row>
     <row r="14" spans="1:20">
       <c r="A14" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="B14" t="s">
         <v>80</v>
@@ -5228,22 +5219,22 @@
     </row>
     <row r="38" spans="1:20">
       <c r="A38" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B38" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C38" t="s">
         <v>20</v>
       </c>
       <c r="D38" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E38" t="s">
-        <v>148</v>
+        <v>187</v>
       </c>
       <c r="F38" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G38" t="s">
         <v>23</v>
@@ -5261,7 +5252,7 @@
         <v>23</v>
       </c>
       <c r="L38" t="s">
-        <v>187</v>
+        <v>23</v>
       </c>
       <c r="M38" t="s">
         <v>23</v>
@@ -5279,21 +5270,21 @@
         <v>23</v>
       </c>
       <c r="R38" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="S38">
         <v>0</v>
       </c>
       <c r="T38" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="39" spans="1:20">
       <c r="A39" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B39" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C39" t="s">
         <v>20</v>
@@ -5302,7 +5293,7 @@
         <v>21</v>
       </c>
       <c r="E39" t="s">
-        <v>190</v>
+        <v>22</v>
       </c>
       <c r="F39" t="s">
         <v>191</v>
@@ -5364,10 +5355,10 @@
         <v>21</v>
       </c>
       <c r="E40" t="s">
-        <v>22</v>
+        <v>194</v>
       </c>
       <c r="F40" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G40" t="s">
         <v>23</v>
@@ -5385,7 +5376,7 @@
         <v>23</v>
       </c>
       <c r="L40" t="s">
-        <v>23</v>
+        <v>196</v>
       </c>
       <c r="M40" t="s">
         <v>23</v>
@@ -5403,33 +5394,33 @@
         <v>23</v>
       </c>
       <c r="R40" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="S40">
         <v>0</v>
       </c>
       <c r="T40" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="41" spans="1:20">
       <c r="A41" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B41" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C41" t="s">
         <v>20</v>
       </c>
       <c r="D41" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E41" t="s">
-        <v>197</v>
+        <v>47</v>
       </c>
       <c r="F41" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G41" t="s">
         <v>23</v>
@@ -5447,7 +5438,7 @@
         <v>23</v>
       </c>
       <c r="L41" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M41" t="s">
         <v>23</v>
@@ -5465,21 +5456,21 @@
         <v>23</v>
       </c>
       <c r="R41" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="S41">
         <v>0</v>
       </c>
       <c r="T41" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="42" spans="1:20">
       <c r="A42" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B42" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C42" t="s">
         <v>20</v>
@@ -5491,7 +5482,7 @@
         <v>47</v>
       </c>
       <c r="F42" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G42" t="s">
         <v>23</v>
@@ -5509,7 +5500,7 @@
         <v>23</v>
       </c>
       <c r="L42" t="s">
-        <v>203</v>
+        <v>23</v>
       </c>
       <c r="M42" t="s">
         <v>23</v>
@@ -5527,13 +5518,13 @@
         <v>23</v>
       </c>
       <c r="R42" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="S42">
         <v>0</v>
       </c>
       <c r="T42" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="43" spans="1:20">
@@ -5547,13 +5538,13 @@
         <v>20</v>
       </c>
       <c r="D43" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E43" t="s">
-        <v>47</v>
+        <v>206</v>
       </c>
       <c r="F43" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G43" t="s">
         <v>23</v>
@@ -5571,7 +5562,7 @@
         <v>23</v>
       </c>
       <c r="L43" t="s">
-        <v>23</v>
+        <v>208</v>
       </c>
       <c r="M43" t="s">
         <v>23</v>
@@ -5589,21 +5580,21 @@
         <v>23</v>
       </c>
       <c r="R43" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="S43">
         <v>0</v>
       </c>
       <c r="T43" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="44" spans="1:20">
       <c r="A44" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B44" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C44" t="s">
         <v>20</v>
@@ -5612,10 +5603,10 @@
         <v>21</v>
       </c>
       <c r="E44" t="s">
-        <v>209</v>
+        <v>88</v>
       </c>
       <c r="F44" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G44" t="s">
         <v>23</v>
@@ -5633,7 +5624,7 @@
         <v>23</v>
       </c>
       <c r="L44" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M44" t="s">
         <v>23</v>
@@ -5662,10 +5653,10 @@
     </row>
     <row r="45" spans="1:20">
       <c r="A45" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B45" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C45" t="s">
         <v>20</v>
@@ -5674,10 +5665,10 @@
         <v>21</v>
       </c>
       <c r="E45" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="F45" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G45" t="s">
         <v>23</v>
@@ -5695,7 +5686,7 @@
         <v>23</v>
       </c>
       <c r="L45" t="s">
-        <v>215</v>
+        <v>23</v>
       </c>
       <c r="M45" t="s">
         <v>23</v>
@@ -5713,13 +5704,13 @@
         <v>23</v>
       </c>
       <c r="R45" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="S45">
         <v>0</v>
       </c>
       <c r="T45" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="46" spans="1:20">
@@ -5736,7 +5727,7 @@
         <v>21</v>
       </c>
       <c r="E46" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="F46" t="s">
         <v>218</v>
@@ -5757,7 +5748,7 @@
         <v>23</v>
       </c>
       <c r="L46" t="s">
-        <v>23</v>
+        <v>219</v>
       </c>
       <c r="M46" t="s">
         <v>23</v>
@@ -5775,21 +5766,21 @@
         <v>23</v>
       </c>
       <c r="R46" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="S46">
         <v>0</v>
       </c>
       <c r="T46" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="47" spans="1:20">
       <c r="A47" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B47" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C47" t="s">
         <v>20</v>
@@ -5798,10 +5789,10 @@
         <v>21</v>
       </c>
       <c r="E47" t="s">
-        <v>38</v>
+        <v>222</v>
       </c>
       <c r="F47" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="G47" t="s">
         <v>23</v>
@@ -5819,7 +5810,7 @@
         <v>23</v>
       </c>
       <c r="L47" t="s">
-        <v>222</v>
+        <v>23</v>
       </c>
       <c r="M47" t="s">
         <v>23</v>
@@ -5837,21 +5828,21 @@
         <v>23</v>
       </c>
       <c r="R47" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="S47">
         <v>0</v>
       </c>
       <c r="T47" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="48" spans="1:20">
       <c r="A48" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B48" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C48" t="s">
         <v>20</v>
@@ -5860,7 +5851,7 @@
         <v>21</v>
       </c>
       <c r="E48" t="s">
-        <v>225</v>
+        <v>38</v>
       </c>
       <c r="F48" t="s">
         <v>226</v>
@@ -5881,7 +5872,7 @@
         <v>23</v>
       </c>
       <c r="L48" t="s">
-        <v>23</v>
+        <v>227</v>
       </c>
       <c r="M48" t="s">
         <v>23</v>
@@ -5899,33 +5890,33 @@
         <v>23</v>
       </c>
       <c r="R48" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="S48">
         <v>0</v>
       </c>
       <c r="T48" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="49" spans="1:20">
       <c r="A49" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B49" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C49" t="s">
         <v>20</v>
       </c>
       <c r="D49" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E49" t="s">
-        <v>38</v>
+        <v>148</v>
       </c>
       <c r="F49" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G49" t="s">
         <v>23</v>
@@ -5943,7 +5934,7 @@
         <v>23</v>
       </c>
       <c r="L49" t="s">
-        <v>230</v>
+        <v>23</v>
       </c>
       <c r="M49" t="s">
         <v>23</v>
@@ -5961,13 +5952,13 @@
         <v>23</v>
       </c>
       <c r="R49" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="S49">
         <v>0</v>
       </c>
       <c r="T49" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="50" spans="1:20">
@@ -5984,7 +5975,7 @@
         <v>42</v>
       </c>
       <c r="E50" t="s">
-        <v>148</v>
+        <v>47</v>
       </c>
       <c r="F50" t="s">
         <v>233</v>
@@ -6005,7 +5996,7 @@
         <v>23</v>
       </c>
       <c r="L50" t="s">
-        <v>23</v>
+        <v>234</v>
       </c>
       <c r="M50" t="s">
         <v>23</v>
@@ -6023,33 +6014,33 @@
         <v>23</v>
       </c>
       <c r="R50" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="S50">
         <v>0</v>
       </c>
       <c r="T50" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
     </row>
     <row r="51" spans="1:20">
       <c r="A51" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B51" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C51" t="s">
         <v>20</v>
       </c>
       <c r="D51" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E51" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="F51" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G51" t="s">
         <v>23</v>
@@ -6067,7 +6058,7 @@
         <v>23</v>
       </c>
       <c r="L51" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M51" t="s">
         <v>23</v>
@@ -6085,21 +6076,21 @@
         <v>23</v>
       </c>
       <c r="R51" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="S51">
         <v>0</v>
       </c>
       <c r="T51" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="52" spans="1:20">
       <c r="A52" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B52" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C52" t="s">
         <v>20</v>
@@ -6108,10 +6099,10 @@
         <v>21</v>
       </c>
       <c r="E52" t="s">
-        <v>22</v>
+        <v>241</v>
       </c>
       <c r="F52" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="G52" t="s">
         <v>23</v>
@@ -6129,7 +6120,7 @@
         <v>23</v>
       </c>
       <c r="L52" t="s">
-        <v>241</v>
+        <v>23</v>
       </c>
       <c r="M52" t="s">
         <v>23</v>
@@ -6147,18 +6138,18 @@
         <v>23</v>
       </c>
       <c r="R52" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="S52">
         <v>0</v>
       </c>
       <c r="T52" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="53" spans="1:20">
       <c r="A53" t="s">
-        <v>242</v>
+        <v>803</v>
       </c>
       <c r="B53" t="s">
         <v>243</v>
@@ -6167,13 +6158,13 @@
         <v>20</v>
       </c>
       <c r="D53" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E53" t="s">
+        <v>69</v>
+      </c>
+      <c r="F53" t="s">
         <v>244</v>
-      </c>
-      <c r="F53" t="s">
-        <v>245</v>
       </c>
       <c r="G53" t="s">
         <v>23</v>
@@ -6220,7 +6211,7 @@
     </row>
     <row r="54" spans="1:20">
       <c r="A54" t="s">
-        <v>806</v>
+        <v>245</v>
       </c>
       <c r="B54" t="s">
         <v>246</v>
@@ -6229,13 +6220,13 @@
         <v>20</v>
       </c>
       <c r="D54" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E54" t="s">
-        <v>69</v>
+        <v>247</v>
       </c>
       <c r="F54" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G54" t="s">
         <v>23</v>
@@ -6271,30 +6262,30 @@
         <v>23</v>
       </c>
       <c r="R54" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="S54">
         <v>0</v>
       </c>
       <c r="T54" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="55" spans="1:20">
       <c r="A55" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B55" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C55" t="s">
         <v>20</v>
       </c>
       <c r="D55" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E55" t="s">
-        <v>250</v>
+        <v>47</v>
       </c>
       <c r="F55" t="s">
         <v>251</v>
@@ -6333,13 +6324,13 @@
         <v>23</v>
       </c>
       <c r="R55" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="S55">
         <v>0</v>
       </c>
       <c r="T55" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="56" spans="1:20">
@@ -6356,7 +6347,7 @@
         <v>42</v>
       </c>
       <c r="E56" t="s">
-        <v>47</v>
+        <v>84</v>
       </c>
       <c r="F56" t="s">
         <v>254</v>
@@ -6377,7 +6368,7 @@
         <v>23</v>
       </c>
       <c r="L56" t="s">
-        <v>23</v>
+        <v>255</v>
       </c>
       <c r="M56" t="s">
         <v>23</v>
@@ -6395,33 +6386,33 @@
         <v>23</v>
       </c>
       <c r="R56" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="S56">
         <v>0</v>
       </c>
       <c r="T56" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
     </row>
     <row r="57" spans="1:20">
       <c r="A57" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B57" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C57" t="s">
         <v>20</v>
       </c>
       <c r="D57" t="s">
-        <v>42</v>
+        <v>154</v>
       </c>
       <c r="E57" t="s">
-        <v>84</v>
+        <v>155</v>
       </c>
       <c r="F57" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G57" t="s">
         <v>23</v>
@@ -6439,7 +6430,7 @@
         <v>23</v>
       </c>
       <c r="L57" t="s">
-        <v>258</v>
+        <v>23</v>
       </c>
       <c r="M57" t="s">
         <v>23</v>
@@ -6457,13 +6448,13 @@
         <v>23</v>
       </c>
       <c r="R57" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="S57">
         <v>0</v>
       </c>
       <c r="T57" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="58" spans="1:20">
@@ -6477,10 +6468,10 @@
         <v>20</v>
       </c>
       <c r="D58" t="s">
-        <v>154</v>
+        <v>21</v>
       </c>
       <c r="E58" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="F58" t="s">
         <v>261</v>
@@ -6501,7 +6492,7 @@
         <v>23</v>
       </c>
       <c r="L58" t="s">
-        <v>23</v>
+        <v>262</v>
       </c>
       <c r="M58" t="s">
         <v>23</v>
@@ -6519,33 +6510,33 @@
         <v>23</v>
       </c>
       <c r="R58" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="S58">
         <v>0</v>
       </c>
       <c r="T58" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="59" spans="1:20">
       <c r="A59" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B59" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C59" t="s">
         <v>20</v>
       </c>
       <c r="D59" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E59" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F59" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G59" t="s">
         <v>23</v>
@@ -6563,7 +6554,7 @@
         <v>23</v>
       </c>
       <c r="L59" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M59" t="s">
         <v>23</v>
@@ -6581,21 +6572,21 @@
         <v>23</v>
       </c>
       <c r="R59" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="S59">
         <v>0</v>
       </c>
       <c r="T59" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="60" spans="1:20">
       <c r="A60" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B60" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C60" t="s">
         <v>20</v>
@@ -6604,10 +6595,10 @@
         <v>42</v>
       </c>
       <c r="E60" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="F60" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G60" t="s">
         <v>23</v>
@@ -6625,7 +6616,7 @@
         <v>23</v>
       </c>
       <c r="L60" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M60" t="s">
         <v>23</v>
@@ -6654,10 +6645,10 @@
     </row>
     <row r="61" spans="1:20">
       <c r="A61" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B61" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C61" t="s">
         <v>20</v>
@@ -6666,10 +6657,10 @@
         <v>42</v>
       </c>
       <c r="E61" t="s">
-        <v>69</v>
+        <v>273</v>
       </c>
       <c r="F61" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G61" t="s">
         <v>23</v>
@@ -6687,7 +6678,7 @@
         <v>23</v>
       </c>
       <c r="L61" t="s">
-        <v>273</v>
+        <v>23</v>
       </c>
       <c r="M61" t="s">
         <v>23</v>
@@ -6705,21 +6696,21 @@
         <v>23</v>
       </c>
       <c r="R61" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="S61">
         <v>0</v>
       </c>
       <c r="T61" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="62" spans="1:20">
       <c r="A62" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B62" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C62" t="s">
         <v>20</v>
@@ -6728,10 +6719,10 @@
         <v>42</v>
       </c>
       <c r="E62" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F62" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G62" t="s">
         <v>23</v>
@@ -6749,7 +6740,7 @@
         <v>23</v>
       </c>
       <c r="L62" t="s">
-        <v>23</v>
+        <v>279</v>
       </c>
       <c r="M62" t="s">
         <v>23</v>
@@ -6767,21 +6758,21 @@
         <v>23</v>
       </c>
       <c r="R62" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="S62">
         <v>0</v>
       </c>
       <c r="T62" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
     </row>
     <row r="63" spans="1:20">
       <c r="A63" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B63" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C63" t="s">
         <v>20</v>
@@ -6790,10 +6781,10 @@
         <v>42</v>
       </c>
       <c r="E63" t="s">
-        <v>280</v>
+        <v>47</v>
       </c>
       <c r="F63" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G63" t="s">
         <v>23</v>
@@ -6811,7 +6802,7 @@
         <v>23</v>
       </c>
       <c r="L63" t="s">
-        <v>282</v>
+        <v>23</v>
       </c>
       <c r="M63" t="s">
         <v>23</v>
@@ -6829,13 +6820,13 @@
         <v>23</v>
       </c>
       <c r="R63" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="S63">
         <v>0</v>
       </c>
       <c r="T63" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="64" spans="1:20">
@@ -6852,7 +6843,7 @@
         <v>42</v>
       </c>
       <c r="E64" t="s">
-        <v>47</v>
+        <v>148</v>
       </c>
       <c r="F64" t="s">
         <v>285</v>
@@ -6911,13 +6902,13 @@
         <v>20</v>
       </c>
       <c r="D65" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E65" t="s">
-        <v>148</v>
+        <v>288</v>
       </c>
       <c r="F65" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G65" t="s">
         <v>23</v>
@@ -6964,19 +6955,19 @@
     </row>
     <row r="66" spans="1:20">
       <c r="A66" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B66" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C66" t="s">
         <v>20</v>
       </c>
       <c r="D66" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E66" t="s">
-        <v>291</v>
+        <v>84</v>
       </c>
       <c r="F66" t="s">
         <v>292</v>
@@ -6997,7 +6988,7 @@
         <v>23</v>
       </c>
       <c r="L66" t="s">
-        <v>23</v>
+        <v>293</v>
       </c>
       <c r="M66" t="s">
         <v>23</v>
@@ -7015,33 +7006,33 @@
         <v>23</v>
       </c>
       <c r="R66" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="S66">
         <v>0</v>
       </c>
       <c r="T66" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
     </row>
     <row r="67" spans="1:20">
       <c r="A67" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B67" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C67" t="s">
         <v>20</v>
       </c>
       <c r="D67" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E67" t="s">
-        <v>84</v>
+        <v>296</v>
       </c>
       <c r="F67" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="G67" t="s">
         <v>23</v>
@@ -7059,7 +7050,7 @@
         <v>23</v>
       </c>
       <c r="L67" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="M67" t="s">
         <v>23</v>
@@ -7077,21 +7068,21 @@
         <v>23</v>
       </c>
       <c r="R67" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="S67">
         <v>0</v>
       </c>
       <c r="T67" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="68" spans="1:20">
       <c r="A68" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B68" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C68" t="s">
         <v>20</v>
@@ -7100,10 +7091,10 @@
         <v>21</v>
       </c>
       <c r="E68" t="s">
-        <v>299</v>
+        <v>22</v>
       </c>
       <c r="F68" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G68" t="s">
         <v>23</v>
@@ -7121,7 +7112,7 @@
         <v>23</v>
       </c>
       <c r="L68" t="s">
-        <v>301</v>
+        <v>23</v>
       </c>
       <c r="M68" t="s">
         <v>23</v>
@@ -7139,13 +7130,13 @@
         <v>23</v>
       </c>
       <c r="R68" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="S68">
         <v>0</v>
       </c>
       <c r="T68" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="69" spans="1:20">
@@ -7183,7 +7174,7 @@
         <v>23</v>
       </c>
       <c r="L69" t="s">
-        <v>23</v>
+        <v>305</v>
       </c>
       <c r="M69" t="s">
         <v>23</v>
@@ -7201,33 +7192,33 @@
         <v>23</v>
       </c>
       <c r="R69" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="S69">
         <v>0</v>
       </c>
       <c r="T69" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="70" spans="1:20">
       <c r="A70" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B70" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C70" t="s">
         <v>20</v>
       </c>
       <c r="D70" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E70" t="s">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c r="F70" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G70" t="s">
         <v>23</v>
@@ -7245,7 +7236,7 @@
         <v>23</v>
       </c>
       <c r="L70" t="s">
-        <v>308</v>
+        <v>23</v>
       </c>
       <c r="M70" t="s">
         <v>23</v>
@@ -7263,13 +7254,13 @@
         <v>23</v>
       </c>
       <c r="R70" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="S70">
         <v>0</v>
       </c>
       <c r="T70" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="71" spans="1:20">
@@ -7283,10 +7274,10 @@
         <v>20</v>
       </c>
       <c r="D71" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E71" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="F71" t="s">
         <v>311</v>
@@ -7307,7 +7298,7 @@
         <v>23</v>
       </c>
       <c r="L71" t="s">
-        <v>23</v>
+        <v>312</v>
       </c>
       <c r="M71" t="s">
         <v>23</v>
@@ -7325,21 +7316,21 @@
         <v>23</v>
       </c>
       <c r="R71" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="S71">
         <v>0</v>
       </c>
       <c r="T71" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="72" spans="1:20">
       <c r="A72" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B72" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C72" t="s">
         <v>20</v>
@@ -7348,10 +7339,10 @@
         <v>21</v>
       </c>
       <c r="E72" t="s">
-        <v>38</v>
+        <v>315</v>
       </c>
       <c r="F72" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="G72" t="s">
         <v>23</v>
@@ -7369,7 +7360,7 @@
         <v>23</v>
       </c>
       <c r="L72" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M72" t="s">
         <v>23</v>
@@ -7398,10 +7389,10 @@
     </row>
     <row r="73" spans="1:20">
       <c r="A73" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B73" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C73" t="s">
         <v>20</v>
@@ -7410,10 +7401,10 @@
         <v>21</v>
       </c>
       <c r="E73" t="s">
-        <v>318</v>
+        <v>38</v>
       </c>
       <c r="F73" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="G73" t="s">
         <v>23</v>
@@ -7431,7 +7422,7 @@
         <v>23</v>
       </c>
       <c r="L73" t="s">
-        <v>320</v>
+        <v>23</v>
       </c>
       <c r="M73" t="s">
         <v>23</v>
@@ -7449,13 +7440,13 @@
         <v>23</v>
       </c>
       <c r="R73" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="S73">
         <v>0</v>
       </c>
       <c r="T73" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="74" spans="1:20">
@@ -7472,7 +7463,7 @@
         <v>21</v>
       </c>
       <c r="E74" t="s">
-        <v>38</v>
+        <v>108</v>
       </c>
       <c r="F74" t="s">
         <v>323</v>
@@ -7531,10 +7522,10 @@
         <v>20</v>
       </c>
       <c r="D75" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E75" t="s">
-        <v>108</v>
+        <v>47</v>
       </c>
       <c r="F75" t="s">
         <v>326</v>
@@ -7555,7 +7546,7 @@
         <v>23</v>
       </c>
       <c r="L75" t="s">
-        <v>23</v>
+        <v>327</v>
       </c>
       <c r="M75" t="s">
         <v>23</v>
@@ -7573,33 +7564,33 @@
         <v>23</v>
       </c>
       <c r="R75" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="S75">
         <v>0</v>
       </c>
       <c r="T75" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
     </row>
     <row r="76" spans="1:20">
       <c r="A76" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B76" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C76" t="s">
         <v>20</v>
       </c>
       <c r="D76" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E76" t="s">
-        <v>47</v>
+        <v>330</v>
       </c>
       <c r="F76" t="s">
-        <v>329</v>
+        <v>23</v>
       </c>
       <c r="G76" t="s">
         <v>23</v>
@@ -7617,7 +7608,7 @@
         <v>23</v>
       </c>
       <c r="L76" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M76" t="s">
         <v>23</v>
@@ -7635,21 +7626,21 @@
         <v>23</v>
       </c>
       <c r="R76" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="S76">
         <v>0</v>
       </c>
       <c r="T76" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="77" spans="1:20">
       <c r="A77" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B77" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C77" t="s">
         <v>20</v>
@@ -7658,10 +7649,10 @@
         <v>21</v>
       </c>
       <c r="E77" t="s">
-        <v>333</v>
+        <v>88</v>
       </c>
       <c r="F77" t="s">
-        <v>23</v>
+        <v>334</v>
       </c>
       <c r="G77" t="s">
         <v>23</v>
@@ -7679,7 +7670,7 @@
         <v>23</v>
       </c>
       <c r="L77" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M77" t="s">
         <v>23</v>
@@ -7708,22 +7699,22 @@
     </row>
     <row r="78" spans="1:20">
       <c r="A78" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B78" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C78" t="s">
         <v>20</v>
       </c>
       <c r="D78" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E78" t="s">
-        <v>88</v>
+        <v>143</v>
       </c>
       <c r="F78" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G78" t="s">
         <v>23</v>
@@ -7741,7 +7732,7 @@
         <v>23</v>
       </c>
       <c r="L78" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M78" t="s">
         <v>23</v>
@@ -7759,21 +7750,21 @@
         <v>23</v>
       </c>
       <c r="R78" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="S78">
         <v>0</v>
       </c>
       <c r="T78" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="79" spans="1:20">
       <c r="A79" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B79" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C79" t="s">
         <v>20</v>
@@ -7782,10 +7773,10 @@
         <v>42</v>
       </c>
       <c r="E79" t="s">
-        <v>143</v>
+        <v>69</v>
       </c>
       <c r="F79" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G79" t="s">
         <v>23</v>
@@ -7803,7 +7794,7 @@
         <v>23</v>
       </c>
       <c r="L79" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M79" t="s">
         <v>23</v>
@@ -7832,10 +7823,10 @@
     </row>
     <row r="80" spans="1:20">
       <c r="A80" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B80" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C80" t="s">
         <v>20</v>
@@ -7844,10 +7835,10 @@
         <v>42</v>
       </c>
       <c r="E80" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="F80" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G80" t="s">
         <v>23</v>
@@ -7865,7 +7856,7 @@
         <v>23</v>
       </c>
       <c r="L80" t="s">
-        <v>346</v>
+        <v>23</v>
       </c>
       <c r="M80" t="s">
         <v>23</v>
@@ -7883,13 +7874,13 @@
         <v>23</v>
       </c>
       <c r="R80" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="S80">
         <v>0</v>
       </c>
       <c r="T80" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="81" spans="1:20">
@@ -7906,7 +7897,7 @@
         <v>42</v>
       </c>
       <c r="E81" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="F81" t="s">
         <v>349</v>
@@ -7927,7 +7918,7 @@
         <v>23</v>
       </c>
       <c r="L81" t="s">
-        <v>23</v>
+        <v>350</v>
       </c>
       <c r="M81" t="s">
         <v>23</v>
@@ -7945,33 +7936,33 @@
         <v>23</v>
       </c>
       <c r="R81" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="S81">
         <v>0</v>
       </c>
       <c r="T81" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
     </row>
     <row r="82" spans="1:20">
       <c r="A82" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B82" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C82" t="s">
         <v>20</v>
       </c>
       <c r="D82" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E82" t="s">
-        <v>93</v>
+        <v>241</v>
       </c>
       <c r="F82" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="G82" t="s">
         <v>23</v>
@@ -7989,7 +7980,7 @@
         <v>23</v>
       </c>
       <c r="L82" t="s">
-        <v>353</v>
+        <v>23</v>
       </c>
       <c r="M82" t="s">
         <v>23</v>
@@ -8007,13 +7998,13 @@
         <v>23</v>
       </c>
       <c r="R82" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="S82">
         <v>0</v>
       </c>
       <c r="T82" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="83" spans="1:20">
@@ -8030,7 +8021,7 @@
         <v>21</v>
       </c>
       <c r="E83" t="s">
-        <v>244</v>
+        <v>64</v>
       </c>
       <c r="F83" t="s">
         <v>356</v>
@@ -8051,7 +8042,7 @@
         <v>23</v>
       </c>
       <c r="L83" t="s">
-        <v>23</v>
+        <v>357</v>
       </c>
       <c r="M83" t="s">
         <v>23</v>
@@ -8069,33 +8060,33 @@
         <v>23</v>
       </c>
       <c r="R83" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="S83">
         <v>0</v>
       </c>
       <c r="T83" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="84" spans="1:20">
       <c r="A84" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B84" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C84" t="s">
         <v>20</v>
       </c>
       <c r="D84" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E84" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="F84" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="G84" t="s">
         <v>23</v>
@@ -8113,7 +8104,7 @@
         <v>23</v>
       </c>
       <c r="L84" t="s">
-        <v>360</v>
+        <v>23</v>
       </c>
       <c r="M84" t="s">
         <v>23</v>
@@ -8131,13 +8122,13 @@
         <v>23</v>
       </c>
       <c r="R84" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="S84">
         <v>0</v>
       </c>
       <c r="T84" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="85" spans="1:20">
@@ -8151,10 +8142,10 @@
         <v>20</v>
       </c>
       <c r="D85" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E85" t="s">
-        <v>84</v>
+        <v>174</v>
       </c>
       <c r="F85" t="s">
         <v>363</v>
@@ -8216,7 +8207,7 @@
         <v>21</v>
       </c>
       <c r="E86" t="s">
-        <v>174</v>
+        <v>38</v>
       </c>
       <c r="F86" t="s">
         <v>366</v>
@@ -8237,7 +8228,7 @@
         <v>23</v>
       </c>
       <c r="L86" t="s">
-        <v>23</v>
+        <v>367</v>
       </c>
       <c r="M86" t="s">
         <v>23</v>
@@ -8255,21 +8246,21 @@
         <v>23</v>
       </c>
       <c r="R86" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="S86">
         <v>0</v>
       </c>
       <c r="T86" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="87" spans="1:20">
       <c r="A87" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B87" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C87" t="s">
         <v>20</v>
@@ -8278,10 +8269,10 @@
         <v>21</v>
       </c>
       <c r="E87" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="F87" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="G87" t="s">
         <v>23</v>
@@ -8299,7 +8290,7 @@
         <v>23</v>
       </c>
       <c r="L87" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M87" t="s">
         <v>23</v>
@@ -8328,10 +8319,10 @@
     </row>
     <row r="88" spans="1:20">
       <c r="A88" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B88" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C88" t="s">
         <v>20</v>
@@ -8340,10 +8331,10 @@
         <v>21</v>
       </c>
       <c r="E88" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="F88" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="G88" t="s">
         <v>23</v>
@@ -8361,7 +8352,7 @@
         <v>23</v>
       </c>
       <c r="L88" t="s">
-        <v>374</v>
+        <v>23</v>
       </c>
       <c r="M88" t="s">
         <v>23</v>
@@ -8379,13 +8370,13 @@
         <v>23</v>
       </c>
       <c r="R88" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="S88">
         <v>0</v>
       </c>
       <c r="T88" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="89" spans="1:20">
@@ -8402,7 +8393,7 @@
         <v>21</v>
       </c>
       <c r="E89" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="F89" t="s">
         <v>378</v>
@@ -8461,10 +8452,10 @@
         <v>20</v>
       </c>
       <c r="D90" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E90" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="F90" t="s">
         <v>381</v>
@@ -8485,7 +8476,7 @@
         <v>23</v>
       </c>
       <c r="L90" t="s">
-        <v>23</v>
+        <v>382</v>
       </c>
       <c r="M90" t="s">
         <v>23</v>
@@ -8503,33 +8494,33 @@
         <v>23</v>
       </c>
       <c r="R90" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="S90">
         <v>0</v>
       </c>
       <c r="T90" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
     </row>
     <row r="91" spans="1:20">
       <c r="A91" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B91" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C91" t="s">
         <v>20</v>
       </c>
       <c r="D91" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E91" t="s">
-        <v>43</v>
+        <v>385</v>
       </c>
       <c r="F91" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="G91" t="s">
         <v>23</v>
@@ -8547,7 +8538,7 @@
         <v>23</v>
       </c>
       <c r="L91" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="M91" t="s">
         <v>23</v>
@@ -8565,33 +8556,33 @@
         <v>23</v>
       </c>
       <c r="R91" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="S91">
         <v>0</v>
       </c>
       <c r="T91" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="92" spans="1:20">
       <c r="A92" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B92" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C92" t="s">
         <v>20</v>
       </c>
       <c r="D92" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E92" t="s">
-        <v>388</v>
+        <v>69</v>
       </c>
       <c r="F92" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G92" t="s">
         <v>23</v>
@@ -8609,7 +8600,7 @@
         <v>23</v>
       </c>
       <c r="L92" t="s">
-        <v>390</v>
+        <v>23</v>
       </c>
       <c r="M92" t="s">
         <v>23</v>
@@ -8627,13 +8618,13 @@
         <v>23</v>
       </c>
       <c r="R92" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="S92">
         <v>0</v>
       </c>
       <c r="T92" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="93" spans="1:20">
@@ -8647,10 +8638,10 @@
         <v>20</v>
       </c>
       <c r="D93" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E93" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="F93" t="s">
         <v>393</v>
@@ -8712,7 +8703,7 @@
         <v>21</v>
       </c>
       <c r="E94" t="s">
-        <v>38</v>
+        <v>241</v>
       </c>
       <c r="F94" t="s">
         <v>396</v>
@@ -8774,10 +8765,10 @@
         <v>21</v>
       </c>
       <c r="E95" t="s">
-        <v>244</v>
+        <v>399</v>
       </c>
       <c r="F95" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="G95" t="s">
         <v>23</v>
@@ -8824,19 +8815,19 @@
     </row>
     <row r="96" spans="1:20">
       <c r="A96" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B96" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C96" t="s">
         <v>20</v>
       </c>
       <c r="D96" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E96" t="s">
-        <v>402</v>
+        <v>69</v>
       </c>
       <c r="F96" t="s">
         <v>403</v>
@@ -8857,7 +8848,7 @@
         <v>23</v>
       </c>
       <c r="L96" t="s">
-        <v>23</v>
+        <v>404</v>
       </c>
       <c r="M96" t="s">
         <v>23</v>
@@ -8875,33 +8866,33 @@
         <v>23</v>
       </c>
       <c r="R96" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="S96">
         <v>0</v>
       </c>
       <c r="T96" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
     </row>
     <row r="97" spans="1:20">
       <c r="A97" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B97" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C97" t="s">
         <v>20</v>
       </c>
       <c r="D97" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E97" t="s">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="F97" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="G97" t="s">
         <v>23</v>
@@ -8919,7 +8910,7 @@
         <v>23</v>
       </c>
       <c r="L97" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M97" t="s">
         <v>23</v>
@@ -8937,21 +8928,21 @@
         <v>23</v>
       </c>
       <c r="R97" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="S97">
         <v>0</v>
       </c>
       <c r="T97" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="98" spans="1:20">
       <c r="A98" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B98" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C98" t="s">
         <v>20</v>
@@ -8960,10 +8951,10 @@
         <v>21</v>
       </c>
       <c r="E98" t="s">
-        <v>22</v>
+        <v>206</v>
       </c>
       <c r="F98" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="G98" t="s">
         <v>23</v>
@@ -8981,7 +8972,7 @@
         <v>23</v>
       </c>
       <c r="L98" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M98" t="s">
         <v>23</v>
@@ -9010,22 +9001,22 @@
     </row>
     <row r="99" spans="1:20">
       <c r="A99" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B99" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C99" t="s">
         <v>20</v>
       </c>
       <c r="D99" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E99" t="s">
-        <v>209</v>
+        <v>47</v>
       </c>
       <c r="F99" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G99" t="s">
         <v>23</v>
@@ -9043,7 +9034,7 @@
         <v>23</v>
       </c>
       <c r="L99" t="s">
-        <v>415</v>
+        <v>23</v>
       </c>
       <c r="M99" t="s">
         <v>23</v>
@@ -9061,13 +9052,13 @@
         <v>23</v>
       </c>
       <c r="R99" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="S99">
         <v>0</v>
       </c>
       <c r="T99" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="100" spans="1:20">
@@ -9081,13 +9072,13 @@
         <v>20</v>
       </c>
       <c r="D100" t="s">
-        <v>42</v>
+        <v>154</v>
       </c>
       <c r="E100" t="s">
-        <v>47</v>
+        <v>418</v>
       </c>
       <c r="F100" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G100" t="s">
         <v>23</v>
@@ -9134,19 +9125,19 @@
     </row>
     <row r="101" spans="1:20">
       <c r="A101" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B101" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C101" t="s">
         <v>20</v>
       </c>
       <c r="D101" t="s">
-        <v>154</v>
+        <v>42</v>
       </c>
       <c r="E101" t="s">
-        <v>421</v>
+        <v>47</v>
       </c>
       <c r="F101" t="s">
         <v>422</v>
@@ -9167,7 +9158,7 @@
         <v>23</v>
       </c>
       <c r="L101" t="s">
-        <v>23</v>
+        <v>423</v>
       </c>
       <c r="M101" t="s">
         <v>23</v>
@@ -9185,33 +9176,33 @@
         <v>23</v>
       </c>
       <c r="R101" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="S101">
         <v>0</v>
       </c>
       <c r="T101" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
     </row>
     <row r="102" spans="1:20">
       <c r="A102" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B102" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C102" t="s">
         <v>20</v>
       </c>
       <c r="D102" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E102" t="s">
-        <v>47</v>
+        <v>426</v>
       </c>
       <c r="F102" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="G102" t="s">
         <v>23</v>
@@ -9229,7 +9220,7 @@
         <v>23</v>
       </c>
       <c r="L102" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="M102" t="s">
         <v>23</v>
@@ -9247,21 +9238,21 @@
         <v>23</v>
       </c>
       <c r="R102" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="S102">
         <v>0</v>
       </c>
       <c r="T102" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="103" spans="1:20">
       <c r="A103" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B103" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C103" t="s">
         <v>20</v>
@@ -9270,10 +9261,10 @@
         <v>21</v>
       </c>
       <c r="E103" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="F103" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="G103" t="s">
         <v>23</v>
@@ -9291,7 +9282,7 @@
         <v>23</v>
       </c>
       <c r="L103" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="M103" t="s">
         <v>23</v>
@@ -9320,22 +9311,22 @@
     </row>
     <row r="104" spans="1:20">
       <c r="A104" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B104" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C104" t="s">
         <v>20</v>
       </c>
       <c r="D104" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E104" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="F104" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="G104" t="s">
         <v>23</v>
@@ -9353,7 +9344,7 @@
         <v>23</v>
       </c>
       <c r="L104" t="s">
-        <v>436</v>
+        <v>23</v>
       </c>
       <c r="M104" t="s">
         <v>23</v>
@@ -9371,30 +9362,30 @@
         <v>23</v>
       </c>
       <c r="R104" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="S104">
         <v>0</v>
       </c>
       <c r="T104" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="105" spans="1:20">
       <c r="A105" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B105" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C105" t="s">
         <v>20</v>
       </c>
       <c r="D105" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E105" t="s">
-        <v>439</v>
+        <v>38</v>
       </c>
       <c r="F105" t="s">
         <v>440</v>
@@ -9453,10 +9444,10 @@
         <v>20</v>
       </c>
       <c r="D106" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E106" t="s">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="F106" t="s">
         <v>443</v>
@@ -9515,10 +9506,10 @@
         <v>20</v>
       </c>
       <c r="D107" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E107" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="F107" t="s">
         <v>446</v>
@@ -9539,7 +9530,7 @@
         <v>23</v>
       </c>
       <c r="L107" t="s">
-        <v>23</v>
+        <v>447</v>
       </c>
       <c r="M107" t="s">
         <v>23</v>
@@ -9557,21 +9548,21 @@
         <v>23</v>
       </c>
       <c r="R107" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="S107">
         <v>0</v>
       </c>
       <c r="T107" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="108" spans="1:20">
       <c r="A108" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B108" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C108" t="s">
         <v>20</v>
@@ -9580,10 +9571,10 @@
         <v>21</v>
       </c>
       <c r="E108" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="F108" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="G108" t="s">
         <v>23</v>
@@ -9601,7 +9592,7 @@
         <v>23</v>
       </c>
       <c r="L108" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M108" t="s">
         <v>23</v>
@@ -9630,22 +9621,22 @@
     </row>
     <row r="109" spans="1:20">
       <c r="A109" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B109" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C109" t="s">
         <v>20</v>
       </c>
       <c r="D109" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E109" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
       <c r="F109" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="G109" t="s">
         <v>23</v>
@@ -9663,7 +9654,7 @@
         <v>23</v>
       </c>
       <c r="L109" t="s">
-        <v>454</v>
+        <v>23</v>
       </c>
       <c r="M109" t="s">
         <v>23</v>
@@ -9681,13 +9672,13 @@
         <v>23</v>
       </c>
       <c r="R109" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="S109">
         <v>0</v>
       </c>
       <c r="T109" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="110" spans="1:20">
@@ -9701,10 +9692,10 @@
         <v>20</v>
       </c>
       <c r="D110" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E110" t="s">
-        <v>93</v>
+        <v>38</v>
       </c>
       <c r="F110" t="s">
         <v>457</v>
@@ -9725,7 +9716,7 @@
         <v>23</v>
       </c>
       <c r="L110" t="s">
-        <v>23</v>
+        <v>458</v>
       </c>
       <c r="M110" t="s">
         <v>23</v>
@@ -9743,21 +9734,21 @@
         <v>23</v>
       </c>
       <c r="R110" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="S110">
         <v>0</v>
       </c>
       <c r="T110" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="111" spans="1:20">
       <c r="A111" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B111" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C111" t="s">
         <v>20</v>
@@ -9766,10 +9757,10 @@
         <v>21</v>
       </c>
       <c r="E111" t="s">
-        <v>38</v>
+        <v>461</v>
       </c>
       <c r="F111" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="G111" t="s">
         <v>23</v>
@@ -9787,7 +9778,7 @@
         <v>23</v>
       </c>
       <c r="L111" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="M111" t="s">
         <v>23</v>
@@ -9816,22 +9807,22 @@
     </row>
     <row r="112" spans="1:20">
       <c r="A112" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B112" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C112" t="s">
         <v>20</v>
       </c>
       <c r="D112" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E112" t="s">
-        <v>464</v>
+        <v>84</v>
       </c>
       <c r="F112" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="G112" t="s">
         <v>23</v>
@@ -9849,7 +9840,7 @@
         <v>23</v>
       </c>
       <c r="L112" t="s">
-        <v>466</v>
+        <v>23</v>
       </c>
       <c r="M112" t="s">
         <v>23</v>
@@ -9867,13 +9858,13 @@
         <v>23</v>
       </c>
       <c r="R112" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="S112">
         <v>0</v>
       </c>
       <c r="T112" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="113" spans="1:20">
@@ -9890,7 +9881,7 @@
         <v>42</v>
       </c>
       <c r="E113" t="s">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="F113" t="s">
         <v>469</v>
@@ -10011,10 +10002,10 @@
         <v>20</v>
       </c>
       <c r="D115" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E115" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="F115" t="s">
         <v>475</v>
@@ -10035,7 +10026,7 @@
         <v>23</v>
       </c>
       <c r="L115" t="s">
-        <v>23</v>
+        <v>476</v>
       </c>
       <c r="M115" t="s">
         <v>23</v>
@@ -10053,21 +10044,21 @@
         <v>23</v>
       </c>
       <c r="R115" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="S115">
         <v>0</v>
       </c>
       <c r="T115" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="116" spans="1:20">
       <c r="A116" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B116" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C116" t="s">
         <v>20</v>
@@ -10079,7 +10070,7 @@
         <v>38</v>
       </c>
       <c r="F116" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="G116" t="s">
         <v>23</v>
@@ -10097,7 +10088,7 @@
         <v>23</v>
       </c>
       <c r="L116" t="s">
-        <v>479</v>
+        <v>23</v>
       </c>
       <c r="M116" t="s">
         <v>23</v>
@@ -10115,13 +10106,13 @@
         <v>23</v>
       </c>
       <c r="R116" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="S116">
         <v>0</v>
       </c>
       <c r="T116" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="117" spans="1:20">
@@ -10135,13 +10126,13 @@
         <v>20</v>
       </c>
       <c r="D117" t="s">
-        <v>21</v>
+        <v>482</v>
       </c>
       <c r="E117" t="s">
-        <v>38</v>
+        <v>483</v>
       </c>
       <c r="F117" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="G117" t="s">
         <v>23</v>
@@ -10188,19 +10179,19 @@
     </row>
     <row r="118" spans="1:20">
       <c r="A118" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B118" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C118" t="s">
         <v>20</v>
       </c>
       <c r="D118" t="s">
-        <v>485</v>
+        <v>42</v>
       </c>
       <c r="E118" t="s">
-        <v>486</v>
+        <v>148</v>
       </c>
       <c r="F118" t="s">
         <v>487</v>
@@ -10221,7 +10212,7 @@
         <v>23</v>
       </c>
       <c r="L118" t="s">
-        <v>23</v>
+        <v>488</v>
       </c>
       <c r="M118" t="s">
         <v>23</v>
@@ -10239,33 +10230,33 @@
         <v>23</v>
       </c>
       <c r="R118" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="S118">
         <v>0</v>
       </c>
       <c r="T118" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="119" spans="1:20">
       <c r="A119" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B119" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C119" t="s">
         <v>20</v>
       </c>
       <c r="D119" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E119" t="s">
-        <v>148</v>
+        <v>431</v>
       </c>
       <c r="F119" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="G119" t="s">
         <v>23</v>
@@ -10283,7 +10274,7 @@
         <v>23</v>
       </c>
       <c r="L119" t="s">
-        <v>491</v>
+        <v>23</v>
       </c>
       <c r="M119" t="s">
         <v>23</v>
@@ -10301,13 +10292,13 @@
         <v>23</v>
       </c>
       <c r="R119" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="S119">
         <v>0</v>
       </c>
       <c r="T119" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="120" spans="1:20">
@@ -10324,7 +10315,7 @@
         <v>21</v>
       </c>
       <c r="E120" t="s">
-        <v>434</v>
+        <v>26</v>
       </c>
       <c r="F120" t="s">
         <v>494</v>
@@ -10383,10 +10374,10 @@
         <v>20</v>
       </c>
       <c r="D121" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E121" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="F121" t="s">
         <v>497</v>
@@ -10445,10 +10436,10 @@
         <v>20</v>
       </c>
       <c r="D122" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E122" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="F122" t="s">
         <v>500</v>
@@ -10469,7 +10460,7 @@
         <v>23</v>
       </c>
       <c r="L122" t="s">
-        <v>23</v>
+        <v>501</v>
       </c>
       <c r="M122" t="s">
         <v>23</v>
@@ -10487,21 +10478,21 @@
         <v>23</v>
       </c>
       <c r="R122" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="S122">
         <v>0</v>
       </c>
       <c r="T122" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="123" spans="1:20">
       <c r="A123" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B123" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C123" t="s">
         <v>20</v>
@@ -10510,10 +10501,10 @@
         <v>21</v>
       </c>
       <c r="E123" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="F123" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="G123" t="s">
         <v>23</v>
@@ -10531,7 +10522,7 @@
         <v>23</v>
       </c>
       <c r="L123" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M123" t="s">
         <v>23</v>
@@ -10560,22 +10551,22 @@
     </row>
     <row r="124" spans="1:20">
       <c r="A124" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B124" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C124" t="s">
         <v>20</v>
       </c>
       <c r="D124" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E124" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="F124" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G124" t="s">
         <v>23</v>
@@ -10593,7 +10584,7 @@
         <v>23</v>
       </c>
       <c r="L124" t="s">
-        <v>508</v>
+        <v>23</v>
       </c>
       <c r="M124" t="s">
         <v>23</v>
@@ -10611,13 +10602,13 @@
         <v>23</v>
       </c>
       <c r="R124" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="S124">
         <v>0</v>
       </c>
       <c r="T124" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="125" spans="1:20">
@@ -10631,10 +10622,10 @@
         <v>20</v>
       </c>
       <c r="D125" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E125" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="F125" t="s">
         <v>511</v>
@@ -10755,10 +10746,10 @@
         <v>20</v>
       </c>
       <c r="D127" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E127" t="s">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="F127" t="s">
         <v>517</v>
@@ -10779,7 +10770,7 @@
         <v>23</v>
       </c>
       <c r="L127" t="s">
-        <v>23</v>
+        <v>518</v>
       </c>
       <c r="M127" t="s">
         <v>23</v>
@@ -10797,21 +10788,21 @@
         <v>23</v>
       </c>
       <c r="R127" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="S127">
         <v>0</v>
       </c>
       <c r="T127" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
     </row>
     <row r="128" spans="1:20">
       <c r="A128" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B128" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C128" t="s">
         <v>20</v>
@@ -10820,10 +10811,10 @@
         <v>42</v>
       </c>
       <c r="E128" t="s">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="F128" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="G128" t="s">
         <v>23</v>
@@ -10841,7 +10832,7 @@
         <v>23</v>
       </c>
       <c r="L128" t="s">
-        <v>521</v>
+        <v>23</v>
       </c>
       <c r="M128" t="s">
         <v>23</v>
@@ -10859,13 +10850,13 @@
         <v>23</v>
       </c>
       <c r="R128" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="S128">
         <v>0</v>
       </c>
       <c r="T128" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="129" spans="1:20">
@@ -10882,7 +10873,7 @@
         <v>42</v>
       </c>
       <c r="E129" t="s">
-        <v>47</v>
+        <v>273</v>
       </c>
       <c r="F129" t="s">
         <v>524</v>
@@ -10941,13 +10932,13 @@
         <v>20</v>
       </c>
       <c r="D130" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E130" t="s">
-        <v>276</v>
+        <v>527</v>
       </c>
       <c r="F130" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="G130" t="s">
         <v>23</v>
@@ -10965,7 +10956,7 @@
         <v>23</v>
       </c>
       <c r="L130" t="s">
-        <v>23</v>
+        <v>529</v>
       </c>
       <c r="M130" t="s">
         <v>23</v>
@@ -10983,33 +10974,33 @@
         <v>23</v>
       </c>
       <c r="R130" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="S130">
         <v>0</v>
       </c>
       <c r="T130" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="131" spans="1:20">
       <c r="A131" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B131" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C131" t="s">
         <v>20</v>
       </c>
       <c r="D131" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E131" t="s">
-        <v>530</v>
+        <v>47</v>
       </c>
       <c r="F131" t="s">
-        <v>531</v>
+        <v>521</v>
       </c>
       <c r="G131" t="s">
         <v>23</v>
@@ -11027,7 +11018,7 @@
         <v>23</v>
       </c>
       <c r="L131" t="s">
-        <v>532</v>
+        <v>23</v>
       </c>
       <c r="M131" t="s">
         <v>23</v>
@@ -11045,21 +11036,21 @@
         <v>23</v>
       </c>
       <c r="R131" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="S131">
         <v>0</v>
       </c>
       <c r="T131" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="132" spans="1:20">
       <c r="A132" t="s">
+        <v>532</v>
+      </c>
+      <c r="B132" t="s">
         <v>533</v>
-      </c>
-      <c r="B132" t="s">
-        <v>534</v>
       </c>
       <c r="C132" t="s">
         <v>20</v>
@@ -11068,72 +11059,72 @@
         <v>42</v>
       </c>
       <c r="E132" t="s">
+        <v>84</v>
+      </c>
+      <c r="F132" t="s">
+        <v>534</v>
+      </c>
+      <c r="G132" t="s">
+        <v>23</v>
+      </c>
+      <c r="H132" t="s">
+        <v>23</v>
+      </c>
+      <c r="I132" t="s">
+        <v>23</v>
+      </c>
+      <c r="J132" t="s">
+        <v>23</v>
+      </c>
+      <c r="K132" t="s">
+        <v>23</v>
+      </c>
+      <c r="L132" t="s">
+        <v>535</v>
+      </c>
+      <c r="M132" t="s">
+        <v>23</v>
+      </c>
+      <c r="N132" t="s">
+        <v>23</v>
+      </c>
+      <c r="O132" t="s">
+        <v>23</v>
+      </c>
+      <c r="P132" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q132" t="s">
+        <v>23</v>
+      </c>
+      <c r="R132" t="s">
+        <v>46</v>
+      </c>
+      <c r="S132">
+        <v>0</v>
+      </c>
+      <c r="T132" t="s">
         <v>47</v>
-      </c>
-      <c r="F132" t="s">
-        <v>524</v>
-      </c>
-      <c r="G132" t="s">
-        <v>23</v>
-      </c>
-      <c r="H132" t="s">
-        <v>23</v>
-      </c>
-      <c r="I132" t="s">
-        <v>23</v>
-      </c>
-      <c r="J132" t="s">
-        <v>23</v>
-      </c>
-      <c r="K132" t="s">
-        <v>23</v>
-      </c>
-      <c r="L132" t="s">
-        <v>23</v>
-      </c>
-      <c r="M132" t="s">
-        <v>23</v>
-      </c>
-      <c r="N132" t="s">
-        <v>23</v>
-      </c>
-      <c r="O132" t="s">
-        <v>23</v>
-      </c>
-      <c r="P132" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q132" t="s">
-        <v>23</v>
-      </c>
-      <c r="R132" t="s">
-        <v>23</v>
-      </c>
-      <c r="S132">
-        <v>0</v>
-      </c>
-      <c r="T132" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="133" spans="1:20">
       <c r="A133" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B133" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C133" t="s">
         <v>20</v>
       </c>
       <c r="D133" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E133" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="F133" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="G133" t="s">
         <v>23</v>
@@ -11151,7 +11142,7 @@
         <v>23</v>
       </c>
       <c r="L133" t="s">
-        <v>538</v>
+        <v>23</v>
       </c>
       <c r="M133" t="s">
         <v>23</v>
@@ -11169,13 +11160,13 @@
         <v>23</v>
       </c>
       <c r="R133" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="S133">
         <v>0</v>
       </c>
       <c r="T133" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="134" spans="1:20">
@@ -11192,7 +11183,7 @@
         <v>21</v>
       </c>
       <c r="E134" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="F134" t="s">
         <v>541</v>
@@ -11254,10 +11245,10 @@
         <v>21</v>
       </c>
       <c r="E135" t="s">
-        <v>22</v>
+        <v>544</v>
       </c>
       <c r="F135" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="G135" t="s">
         <v>23</v>
@@ -11275,16 +11266,16 @@
         <v>23</v>
       </c>
       <c r="L135" t="s">
-        <v>23</v>
+        <v>546</v>
       </c>
       <c r="M135" t="s">
-        <v>23</v>
+        <v>547</v>
       </c>
       <c r="N135" t="s">
-        <v>23</v>
+        <v>548</v>
       </c>
       <c r="O135" t="s">
-        <v>23</v>
+        <v>549</v>
       </c>
       <c r="P135" t="s">
         <v>23</v>
@@ -11293,21 +11284,21 @@
         <v>23</v>
       </c>
       <c r="R135" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="S135">
         <v>0</v>
       </c>
       <c r="T135" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="136" spans="1:20">
       <c r="A136" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="B136" t="s">
-        <v>546</v>
+        <v>23</v>
       </c>
       <c r="C136" t="s">
         <v>20</v>
@@ -11316,10 +11307,10 @@
         <v>21</v>
       </c>
       <c r="E136" t="s">
-        <v>547</v>
+        <v>431</v>
       </c>
       <c r="F136" t="s">
-        <v>548</v>
+        <v>23</v>
       </c>
       <c r="G136" t="s">
         <v>23</v>
@@ -11337,16 +11328,16 @@
         <v>23</v>
       </c>
       <c r="L136" t="s">
-        <v>549</v>
+        <v>23</v>
       </c>
       <c r="M136" t="s">
-        <v>550</v>
+        <v>23</v>
       </c>
       <c r="N136" t="s">
-        <v>551</v>
+        <v>23</v>
       </c>
       <c r="O136" t="s">
-        <v>552</v>
+        <v>23</v>
       </c>
       <c r="P136" t="s">
         <v>23</v>
@@ -11366,23 +11357,23 @@
     </row>
     <row r="137" spans="1:20">
       <c r="A137" t="s">
+        <v>551</v>
+      </c>
+      <c r="B137" t="s">
+        <v>552</v>
+      </c>
+      <c r="C137" t="s">
+        <v>20</v>
+      </c>
+      <c r="D137" t="s">
+        <v>42</v>
+      </c>
+      <c r="E137" t="s">
+        <v>93</v>
+      </c>
+      <c r="F137" t="s">
         <v>553</v>
       </c>
-      <c r="B137" t="s">
-        <v>23</v>
-      </c>
-      <c r="C137" t="s">
-        <v>20</v>
-      </c>
-      <c r="D137" t="s">
-        <v>21</v>
-      </c>
-      <c r="E137" t="s">
-        <v>434</v>
-      </c>
-      <c r="F137" t="s">
-        <v>23</v>
-      </c>
       <c r="G137" t="s">
         <v>23</v>
       </c>
@@ -11417,13 +11408,13 @@
         <v>23</v>
       </c>
       <c r="R137" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="S137">
         <v>0</v>
       </c>
       <c r="T137" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="138" spans="1:20">
@@ -11440,7 +11431,7 @@
         <v>42</v>
       </c>
       <c r="E138" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="F138" t="s">
         <v>556</v>
@@ -11461,7 +11452,7 @@
         <v>23</v>
       </c>
       <c r="L138" t="s">
-        <v>23</v>
+        <v>557</v>
       </c>
       <c r="M138" t="s">
         <v>23</v>
@@ -11490,22 +11481,22 @@
     </row>
     <row r="139" spans="1:20">
       <c r="A139" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B139" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C139" t="s">
         <v>20</v>
       </c>
       <c r="D139" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E139" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="F139" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="G139" t="s">
         <v>23</v>
@@ -11523,7 +11514,7 @@
         <v>23</v>
       </c>
       <c r="L139" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M139" t="s">
         <v>23</v>
@@ -11541,21 +11532,21 @@
         <v>23</v>
       </c>
       <c r="R139" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="S139">
         <v>0</v>
       </c>
       <c r="T139" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="140" spans="1:20">
       <c r="A140" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B140" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C140" t="s">
         <v>20</v>
@@ -11564,10 +11555,10 @@
         <v>21</v>
       </c>
       <c r="E140" t="s">
-        <v>38</v>
+        <v>564</v>
       </c>
       <c r="F140" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="G140" t="s">
         <v>23</v>
@@ -11585,7 +11576,7 @@
         <v>23</v>
       </c>
       <c r="L140" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="M140" t="s">
         <v>23</v>
@@ -11614,10 +11605,10 @@
     </row>
     <row r="141" spans="1:20">
       <c r="A141" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B141" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C141" t="s">
         <v>20</v>
@@ -11626,10 +11617,10 @@
         <v>21</v>
       </c>
       <c r="E141" t="s">
-        <v>567</v>
+        <v>296</v>
       </c>
       <c r="F141" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="G141" t="s">
         <v>23</v>
@@ -11647,7 +11638,7 @@
         <v>23</v>
       </c>
       <c r="L141" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M141" t="s">
         <v>23</v>
@@ -11676,22 +11667,22 @@
     </row>
     <row r="142" spans="1:20">
       <c r="A142" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B142" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C142" t="s">
         <v>20</v>
       </c>
       <c r="D142" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E142" t="s">
-        <v>299</v>
+        <v>148</v>
       </c>
       <c r="F142" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="G142" t="s">
         <v>23</v>
@@ -11709,7 +11700,7 @@
         <v>23</v>
       </c>
       <c r="L142" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="M142" t="s">
         <v>23</v>
@@ -11727,21 +11718,21 @@
         <v>23</v>
       </c>
       <c r="R142" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="S142">
         <v>0</v>
       </c>
       <c r="T142" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="143" spans="1:20">
       <c r="A143" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B143" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C143" t="s">
         <v>20</v>
@@ -11750,10 +11741,10 @@
         <v>42</v>
       </c>
       <c r="E143" t="s">
-        <v>148</v>
+        <v>69</v>
       </c>
       <c r="F143" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="G143" t="s">
         <v>23</v>
@@ -11771,7 +11762,7 @@
         <v>23</v>
       </c>
       <c r="L143" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M143" t="s">
         <v>23</v>
@@ -11800,22 +11791,22 @@
     </row>
     <row r="144" spans="1:20">
       <c r="A144" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B144" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C144" t="s">
         <v>20</v>
       </c>
       <c r="D144" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E144" t="s">
-        <v>69</v>
+        <v>581</v>
       </c>
       <c r="F144" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="G144" t="s">
         <v>23</v>
@@ -11833,7 +11824,7 @@
         <v>23</v>
       </c>
       <c r="L144" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="M144" t="s">
         <v>23</v>
@@ -11851,21 +11842,21 @@
         <v>23</v>
       </c>
       <c r="R144" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="S144">
         <v>0</v>
       </c>
       <c r="T144" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="145" spans="1:20">
       <c r="A145" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B145" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C145" t="s">
         <v>20</v>
@@ -11874,10 +11865,10 @@
         <v>21</v>
       </c>
       <c r="E145" t="s">
-        <v>584</v>
+        <v>38</v>
       </c>
       <c r="F145" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="G145" t="s">
         <v>23</v>
@@ -11895,7 +11886,7 @@
         <v>23</v>
       </c>
       <c r="L145" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="M145" t="s">
         <v>23</v>
@@ -11924,10 +11915,10 @@
     </row>
     <row r="146" spans="1:20">
       <c r="A146" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B146" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C146" t="s">
         <v>20</v>
@@ -11939,7 +11930,7 @@
         <v>38</v>
       </c>
       <c r="F146" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="G146" t="s">
         <v>23</v>
@@ -11957,7 +11948,7 @@
         <v>23</v>
       </c>
       <c r="L146" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M146" t="s">
         <v>23</v>
@@ -11986,10 +11977,10 @@
     </row>
     <row r="147" spans="1:20">
       <c r="A147" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B147" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C147" t="s">
         <v>20</v>
@@ -11998,10 +11989,10 @@
         <v>21</v>
       </c>
       <c r="E147" t="s">
-        <v>38</v>
+        <v>594</v>
       </c>
       <c r="F147" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="G147" t="s">
         <v>23</v>
@@ -12019,7 +12010,7 @@
         <v>23</v>
       </c>
       <c r="L147" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="M147" t="s">
         <v>23</v>
@@ -12048,10 +12039,10 @@
     </row>
     <row r="148" spans="1:20">
       <c r="A148" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B148" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C148" t="s">
         <v>20</v>
@@ -12060,10 +12051,10 @@
         <v>21</v>
       </c>
       <c r="E148" t="s">
-        <v>597</v>
+        <v>108</v>
       </c>
       <c r="F148" t="s">
-        <v>598</v>
+        <v>323</v>
       </c>
       <c r="G148" t="s">
         <v>23</v>
@@ -12119,13 +12110,13 @@
         <v>20</v>
       </c>
       <c r="D149" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E149" t="s">
-        <v>108</v>
+        <v>143</v>
       </c>
       <c r="F149" t="s">
-        <v>326</v>
+        <v>602</v>
       </c>
       <c r="G149" t="s">
         <v>23</v>
@@ -12143,7 +12134,7 @@
         <v>23</v>
       </c>
       <c r="L149" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M149" t="s">
         <v>23</v>
@@ -12161,33 +12152,33 @@
         <v>23</v>
       </c>
       <c r="R149" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="S149">
         <v>0</v>
       </c>
       <c r="T149" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="150" spans="1:20">
       <c r="A150" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B150" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C150" t="s">
         <v>20</v>
       </c>
       <c r="D150" t="s">
-        <v>42</v>
+        <v>372</v>
       </c>
       <c r="E150" t="s">
-        <v>143</v>
+        <v>606</v>
       </c>
       <c r="F150" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="G150" t="s">
         <v>23</v>
@@ -12205,7 +12196,7 @@
         <v>23</v>
       </c>
       <c r="L150" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="M150" t="s">
         <v>23</v>
@@ -12223,33 +12214,33 @@
         <v>23</v>
       </c>
       <c r="R150" t="s">
-        <v>46</v>
+        <v>609</v>
       </c>
       <c r="S150">
         <v>0</v>
       </c>
       <c r="T150" t="s">
-        <v>47</v>
+        <v>610</v>
       </c>
     </row>
     <row r="151" spans="1:20">
       <c r="A151" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="B151" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="C151" t="s">
         <v>20</v>
       </c>
       <c r="D151" t="s">
-        <v>375</v>
+        <v>42</v>
       </c>
       <c r="E151" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="F151" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="G151" t="s">
         <v>23</v>
@@ -12267,7 +12258,7 @@
         <v>23</v>
       </c>
       <c r="L151" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="M151" t="s">
         <v>23</v>
@@ -12285,33 +12276,33 @@
         <v>23</v>
       </c>
       <c r="R151" t="s">
-        <v>612</v>
+        <v>46</v>
       </c>
       <c r="S151">
         <v>0</v>
       </c>
       <c r="T151" t="s">
-        <v>613</v>
+        <v>47</v>
       </c>
     </row>
     <row r="152" spans="1:20">
       <c r="A152" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B152" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C152" t="s">
         <v>20</v>
       </c>
       <c r="D152" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E152" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="F152" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="G152" t="s">
         <v>23</v>
@@ -12329,7 +12320,7 @@
         <v>23</v>
       </c>
       <c r="L152" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="M152" t="s">
         <v>23</v>
@@ -12347,33 +12338,33 @@
         <v>23</v>
       </c>
       <c r="R152" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="S152">
         <v>0</v>
       </c>
       <c r="T152" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="153" spans="1:20">
       <c r="A153" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="B153" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="C153" t="s">
         <v>20</v>
       </c>
       <c r="D153" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E153" t="s">
-        <v>621</v>
+        <v>47</v>
       </c>
       <c r="F153" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="G153" t="s">
         <v>23</v>
@@ -12391,7 +12382,7 @@
         <v>23</v>
       </c>
       <c r="L153" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="M153" t="s">
         <v>23</v>
@@ -12409,33 +12400,33 @@
         <v>23</v>
       </c>
       <c r="R153" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="S153">
         <v>0</v>
       </c>
       <c r="T153" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="154" spans="1:20">
       <c r="A154" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B154" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C154" t="s">
         <v>20</v>
       </c>
       <c r="D154" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E154" t="s">
-        <v>47</v>
+        <v>627</v>
       </c>
       <c r="F154" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="G154" t="s">
         <v>23</v>
@@ -12453,7 +12444,7 @@
         <v>23</v>
       </c>
       <c r="L154" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="M154" t="s">
         <v>23</v>
@@ -12471,33 +12462,33 @@
         <v>23</v>
       </c>
       <c r="R154" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="S154">
         <v>0</v>
       </c>
       <c r="T154" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="155" spans="1:20">
       <c r="A155" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="B155" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C155" t="s">
         <v>20</v>
       </c>
       <c r="D155" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E155" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="F155" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="G155" t="s">
         <v>23</v>
@@ -12515,7 +12506,7 @@
         <v>23</v>
       </c>
       <c r="L155" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="M155" t="s">
         <v>23</v>
@@ -12533,33 +12524,33 @@
         <v>23</v>
       </c>
       <c r="R155" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="S155">
         <v>0</v>
       </c>
       <c r="T155" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="156" spans="1:20">
       <c r="A156" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="B156" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="C156" t="s">
         <v>20</v>
       </c>
       <c r="D156" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E156" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="F156" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="G156" t="s">
         <v>23</v>
@@ -12577,7 +12568,7 @@
         <v>23</v>
       </c>
       <c r="L156" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="M156" t="s">
         <v>23</v>
@@ -12595,21 +12586,21 @@
         <v>23</v>
       </c>
       <c r="R156" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="S156">
         <v>0</v>
       </c>
       <c r="T156" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="157" spans="1:20">
       <c r="A157" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B157" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="C157" t="s">
         <v>20</v>
@@ -12618,10 +12609,10 @@
         <v>21</v>
       </c>
       <c r="E157" t="s">
-        <v>640</v>
+        <v>26</v>
       </c>
       <c r="F157" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="G157" t="s">
         <v>23</v>
@@ -12639,7 +12630,7 @@
         <v>23</v>
       </c>
       <c r="L157" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="M157" t="s">
         <v>23</v>
@@ -12668,10 +12659,10 @@
     </row>
     <row r="158" spans="1:20">
       <c r="A158" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B158" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C158" t="s">
         <v>20</v>
@@ -12680,10 +12671,10 @@
         <v>21</v>
       </c>
       <c r="E158" t="s">
-        <v>26</v>
+        <v>241</v>
       </c>
       <c r="F158" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="G158" t="s">
         <v>23</v>
@@ -12701,7 +12692,7 @@
         <v>23</v>
       </c>
       <c r="L158" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="M158" t="s">
         <v>23</v>
@@ -12719,33 +12710,33 @@
         <v>23</v>
       </c>
       <c r="R158" t="s">
-        <v>29</v>
+        <v>609</v>
       </c>
       <c r="S158">
         <v>0</v>
       </c>
       <c r="T158" t="s">
-        <v>30</v>
+        <v>610</v>
       </c>
     </row>
     <row r="159" spans="1:20">
       <c r="A159" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B159" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C159" t="s">
         <v>20</v>
       </c>
       <c r="D159" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E159" t="s">
-        <v>244</v>
+        <v>650</v>
       </c>
       <c r="F159" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="G159" t="s">
         <v>23</v>
@@ -12763,7 +12754,7 @@
         <v>23</v>
       </c>
       <c r="L159" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="M159" t="s">
         <v>23</v>
@@ -12781,33 +12772,33 @@
         <v>23</v>
       </c>
       <c r="R159" t="s">
-        <v>612</v>
+        <v>46</v>
       </c>
       <c r="S159">
         <v>0</v>
       </c>
       <c r="T159" t="s">
-        <v>613</v>
+        <v>47</v>
       </c>
     </row>
     <row r="160" spans="1:20">
       <c r="A160" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="B160" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="C160" t="s">
         <v>20</v>
       </c>
       <c r="D160" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E160" t="s">
-        <v>653</v>
+        <v>88</v>
       </c>
       <c r="F160" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="G160" t="s">
         <v>23</v>
@@ -12825,7 +12816,7 @@
         <v>23</v>
       </c>
       <c r="L160" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="M160" t="s">
         <v>23</v>
@@ -12843,21 +12834,21 @@
         <v>23</v>
       </c>
       <c r="R160" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="S160">
         <v>0</v>
       </c>
       <c r="T160" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="161" spans="1:20">
       <c r="A161" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B161" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C161" t="s">
         <v>20</v>
@@ -12866,10 +12857,10 @@
         <v>21</v>
       </c>
       <c r="E161" t="s">
-        <v>88</v>
+        <v>138</v>
       </c>
       <c r="F161" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="G161" t="s">
         <v>23</v>
@@ -12887,7 +12878,7 @@
         <v>23</v>
       </c>
       <c r="L161" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="M161" t="s">
         <v>23</v>
@@ -12916,10 +12907,10 @@
     </row>
     <row r="162" spans="1:20">
       <c r="A162" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B162" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C162" t="s">
         <v>20</v>
@@ -12928,10 +12919,10 @@
         <v>21</v>
       </c>
       <c r="E162" t="s">
-        <v>138</v>
+        <v>38</v>
       </c>
       <c r="F162" t="s">
-        <v>662</v>
+        <v>538</v>
       </c>
       <c r="G162" t="s">
         <v>23</v>
@@ -12993,7 +12984,7 @@
         <v>38</v>
       </c>
       <c r="F163" t="s">
-        <v>541</v>
+        <v>666</v>
       </c>
       <c r="G163" t="s">
         <v>23</v>
@@ -13011,7 +13002,7 @@
         <v>23</v>
       </c>
       <c r="L163" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="M163" t="s">
         <v>23</v>
@@ -13040,22 +13031,22 @@
     </row>
     <row r="164" spans="1:20">
       <c r="A164" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B164" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C164" t="s">
         <v>20</v>
       </c>
       <c r="D164" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E164" t="s">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="F164" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="G164" t="s">
         <v>23</v>
@@ -13073,7 +13064,7 @@
         <v>23</v>
       </c>
       <c r="L164" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="M164" t="s">
         <v>23</v>
@@ -13091,33 +13082,33 @@
         <v>23</v>
       </c>
       <c r="R164" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="S164">
         <v>0</v>
       </c>
       <c r="T164" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="165" spans="1:20">
       <c r="A165" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B165" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C165" t="s">
         <v>20</v>
       </c>
       <c r="D165" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E165" t="s">
-        <v>84</v>
+        <v>22</v>
       </c>
       <c r="F165" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="G165" t="s">
         <v>23</v>
@@ -13135,7 +13126,7 @@
         <v>23</v>
       </c>
       <c r="L165" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="M165" t="s">
         <v>23</v>
@@ -13153,33 +13144,33 @@
         <v>23</v>
       </c>
       <c r="R165" t="s">
-        <v>46</v>
+        <v>609</v>
       </c>
       <c r="S165">
         <v>0</v>
       </c>
       <c r="T165" t="s">
-        <v>47</v>
+        <v>610</v>
       </c>
     </row>
     <row r="166" spans="1:20">
       <c r="A166" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B166" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C166" t="s">
         <v>20</v>
       </c>
       <c r="D166" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E166" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="F166" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="G166" t="s">
         <v>23</v>
@@ -13197,7 +13188,7 @@
         <v>23</v>
       </c>
       <c r="L166" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="M166" t="s">
         <v>23</v>
@@ -13215,33 +13206,33 @@
         <v>23</v>
       </c>
       <c r="R166" t="s">
-        <v>612</v>
+        <v>46</v>
       </c>
       <c r="S166">
         <v>0</v>
       </c>
       <c r="T166" t="s">
-        <v>613</v>
+        <v>47</v>
       </c>
     </row>
     <row r="167" spans="1:20">
       <c r="A167" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B167" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C167" t="s">
         <v>20</v>
       </c>
       <c r="D167" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E167" t="s">
-        <v>47</v>
+        <v>174</v>
       </c>
       <c r="F167" t="s">
-        <v>681</v>
+        <v>545</v>
       </c>
       <c r="G167" t="s">
         <v>23</v>
@@ -13277,13 +13268,13 @@
         <v>23</v>
       </c>
       <c r="R167" t="s">
-        <v>46</v>
+        <v>609</v>
       </c>
       <c r="S167">
         <v>0</v>
       </c>
       <c r="T167" t="s">
-        <v>47</v>
+        <v>610</v>
       </c>
     </row>
     <row r="168" spans="1:20">
@@ -13297,13 +13288,13 @@
         <v>20</v>
       </c>
       <c r="D168" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E168" t="s">
-        <v>174</v>
+        <v>148</v>
       </c>
       <c r="F168" t="s">
-        <v>548</v>
+        <v>685</v>
       </c>
       <c r="G168" t="s">
         <v>23</v>
@@ -13321,7 +13312,7 @@
         <v>23</v>
       </c>
       <c r="L168" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="M168" t="s">
         <v>23</v>
@@ -13339,18 +13330,18 @@
         <v>23</v>
       </c>
       <c r="R168" t="s">
-        <v>612</v>
+        <v>46</v>
       </c>
       <c r="S168">
         <v>0</v>
       </c>
       <c r="T168" t="s">
-        <v>613</v>
+        <v>47</v>
       </c>
     </row>
     <row r="169" spans="1:20">
       <c r="A169" t="s">
-        <v>686</v>
+        <v>123</v>
       </c>
       <c r="B169" t="s">
         <v>687</v>
@@ -13362,10 +13353,10 @@
         <v>42</v>
       </c>
       <c r="E169" t="s">
-        <v>148</v>
+        <v>84</v>
       </c>
       <c r="F169" t="s">
-        <v>688</v>
+        <v>244</v>
       </c>
       <c r="G169" t="s">
         <v>23</v>
@@ -13383,7 +13374,7 @@
         <v>23</v>
       </c>
       <c r="L169" t="s">
-        <v>689</v>
+        <v>126</v>
       </c>
       <c r="M169" t="s">
         <v>23</v>
@@ -13412,23 +13403,23 @@
     </row>
     <row r="170" spans="1:20">
       <c r="A170" t="s">
-        <v>123</v>
+        <v>688</v>
       </c>
       <c r="B170" t="s">
+        <v>689</v>
+      </c>
+      <c r="C170" t="s">
+        <v>20</v>
+      </c>
+      <c r="D170" t="s">
+        <v>21</v>
+      </c>
+      <c r="E170" t="s">
+        <v>38</v>
+      </c>
+      <c r="F170" t="s">
         <v>690</v>
       </c>
-      <c r="C170" t="s">
-        <v>20</v>
-      </c>
-      <c r="D170" t="s">
-        <v>42</v>
-      </c>
-      <c r="E170" t="s">
-        <v>84</v>
-      </c>
-      <c r="F170" t="s">
-        <v>247</v>
-      </c>
       <c r="G170" t="s">
         <v>23</v>
       </c>
@@ -13445,7 +13436,7 @@
         <v>23</v>
       </c>
       <c r="L170" t="s">
-        <v>126</v>
+        <v>23</v>
       </c>
       <c r="M170" t="s">
         <v>23</v>
@@ -13463,13 +13454,13 @@
         <v>23</v>
       </c>
       <c r="R170" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="S170">
         <v>0</v>
       </c>
       <c r="T170" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="171" spans="1:20">
@@ -13486,7 +13477,7 @@
         <v>21</v>
       </c>
       <c r="E171" t="s">
-        <v>38</v>
+        <v>436</v>
       </c>
       <c r="F171" t="s">
         <v>693</v>
@@ -13548,7 +13539,7 @@
         <v>21</v>
       </c>
       <c r="E172" t="s">
-        <v>439</v>
+        <v>64</v>
       </c>
       <c r="F172" t="s">
         <v>696</v>
@@ -13607,10 +13598,10 @@
         <v>20</v>
       </c>
       <c r="D173" t="s">
-        <v>21</v>
+        <v>154</v>
       </c>
       <c r="E173" t="s">
-        <v>64</v>
+        <v>418</v>
       </c>
       <c r="F173" t="s">
         <v>699</v>
@@ -13669,10 +13660,10 @@
         <v>20</v>
       </c>
       <c r="D174" t="s">
-        <v>154</v>
+        <v>21</v>
       </c>
       <c r="E174" t="s">
-        <v>421</v>
+        <v>399</v>
       </c>
       <c r="F174" t="s">
         <v>702</v>
@@ -13731,13 +13722,13 @@
         <v>20</v>
       </c>
       <c r="D175" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E175" t="s">
-        <v>402</v>
+        <v>705</v>
       </c>
       <c r="F175" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G175" t="s">
         <v>23</v>
@@ -13784,19 +13775,19 @@
     </row>
     <row r="176" spans="1:20">
       <c r="A176" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B176" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C176" t="s">
         <v>20</v>
       </c>
       <c r="D176" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E176" t="s">
-        <v>708</v>
+        <v>22</v>
       </c>
       <c r="F176" t="s">
         <v>709</v>
@@ -13846,22 +13837,22 @@
     </row>
     <row r="177" spans="1:20">
       <c r="A177" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B177" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="C177" t="s">
         <v>20</v>
       </c>
       <c r="D177" t="s">
-        <v>21</v>
+        <v>372</v>
       </c>
       <c r="E177" t="s">
-        <v>22</v>
+        <v>606</v>
       </c>
       <c r="F177" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="G177" t="s">
         <v>23</v>
@@ -13911,19 +13902,19 @@
         <v>715</v>
       </c>
       <c r="B178" t="s">
+        <v>184</v>
+      </c>
+      <c r="C178" t="s">
+        <v>20</v>
+      </c>
+      <c r="D178" t="s">
+        <v>42</v>
+      </c>
+      <c r="E178" t="s">
+        <v>148</v>
+      </c>
+      <c r="F178" t="s">
         <v>716</v>
-      </c>
-      <c r="C178" t="s">
-        <v>20</v>
-      </c>
-      <c r="D178" t="s">
-        <v>375</v>
-      </c>
-      <c r="E178" t="s">
-        <v>609</v>
-      </c>
-      <c r="F178" t="s">
-        <v>717</v>
       </c>
       <c r="G178" t="s">
         <v>23</v>
@@ -13970,19 +13961,19 @@
     </row>
     <row r="179" spans="1:20">
       <c r="A179" t="s">
+        <v>717</v>
+      </c>
+      <c r="B179" t="s">
         <v>718</v>
       </c>
-      <c r="B179" t="s">
-        <v>185</v>
-      </c>
       <c r="C179" t="s">
         <v>20</v>
       </c>
       <c r="D179" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E179" t="s">
-        <v>148</v>
+        <v>22</v>
       </c>
       <c r="F179" t="s">
         <v>719</v>
@@ -14003,7 +13994,7 @@
         <v>23</v>
       </c>
       <c r="L179" t="s">
-        <v>23</v>
+        <v>720</v>
       </c>
       <c r="M179" t="s">
         <v>23</v>
@@ -14032,10 +14023,10 @@
     </row>
     <row r="180" spans="1:20">
       <c r="A180" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B180" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C180" t="s">
         <v>20</v>
@@ -14044,10 +14035,10 @@
         <v>21</v>
       </c>
       <c r="E180" t="s">
-        <v>22</v>
+        <v>187</v>
       </c>
       <c r="F180" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="G180" t="s">
         <v>23</v>
@@ -14065,7 +14056,7 @@
         <v>23</v>
       </c>
       <c r="L180" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="M180" t="s">
         <v>23</v>
@@ -14094,10 +14085,10 @@
     </row>
     <row r="181" spans="1:20">
       <c r="A181" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B181" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C181" t="s">
         <v>20</v>
@@ -14106,10 +14097,10 @@
         <v>21</v>
       </c>
       <c r="E181" t="s">
-        <v>190</v>
+        <v>22</v>
       </c>
       <c r="F181" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="G181" t="s">
         <v>23</v>
@@ -14127,7 +14118,7 @@
         <v>23</v>
       </c>
       <c r="L181" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="M181" t="s">
         <v>23</v>
@@ -14156,22 +14147,22 @@
     </row>
     <row r="182" spans="1:20">
       <c r="A182" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B182" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C182" t="s">
         <v>20</v>
       </c>
       <c r="D182" t="s">
-        <v>21</v>
+        <v>482</v>
       </c>
       <c r="E182" t="s">
-        <v>22</v>
+        <v>483</v>
       </c>
       <c r="F182" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="G182" t="s">
         <v>23</v>
@@ -14189,7 +14180,7 @@
         <v>23</v>
       </c>
       <c r="L182" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="M182" t="s">
         <v>23</v>
@@ -14218,22 +14209,22 @@
     </row>
     <row r="183" spans="1:20">
       <c r="A183" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B183" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C183" t="s">
         <v>20</v>
       </c>
       <c r="D183" t="s">
-        <v>485</v>
+        <v>21</v>
       </c>
       <c r="E183" t="s">
-        <v>486</v>
+        <v>38</v>
       </c>
       <c r="F183" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="G183" t="s">
         <v>23</v>
@@ -14251,7 +14242,7 @@
         <v>23</v>
       </c>
       <c r="L183" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="M183" t="s">
         <v>23</v>
@@ -14280,10 +14271,10 @@
     </row>
     <row r="184" spans="1:20">
       <c r="A184" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B184" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C184" t="s">
         <v>20</v>
@@ -14292,10 +14283,10 @@
         <v>21</v>
       </c>
       <c r="E184" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="F184" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="G184" t="s">
         <v>23</v>
@@ -14313,7 +14304,7 @@
         <v>23</v>
       </c>
       <c r="L184" t="s">
-        <v>739</v>
+        <v>23</v>
       </c>
       <c r="M184" t="s">
         <v>23</v>
@@ -14354,10 +14345,10 @@
         <v>21</v>
       </c>
       <c r="E185" t="s">
-        <v>22</v>
+        <v>742</v>
       </c>
       <c r="F185" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="G185" t="s">
         <v>23</v>
@@ -14375,7 +14366,7 @@
         <v>23</v>
       </c>
       <c r="L185" t="s">
-        <v>23</v>
+        <v>744</v>
       </c>
       <c r="M185" t="s">
         <v>23</v>
@@ -14404,10 +14395,10 @@
     </row>
     <row r="186" spans="1:20">
       <c r="A186" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="B186" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="C186" t="s">
         <v>20</v>
@@ -14416,10 +14407,10 @@
         <v>21</v>
       </c>
       <c r="E186" t="s">
-        <v>745</v>
+        <v>22</v>
       </c>
       <c r="F186" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="G186" t="s">
         <v>23</v>
@@ -14437,7 +14428,7 @@
         <v>23</v>
       </c>
       <c r="L186" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="M186" t="s">
         <v>23</v>
@@ -14466,10 +14457,10 @@
     </row>
     <row r="187" spans="1:20">
       <c r="A187" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B187" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C187" t="s">
         <v>20</v>
@@ -14478,10 +14469,10 @@
         <v>21</v>
       </c>
       <c r="E187" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="F187" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="G187" t="s">
         <v>23</v>
@@ -14499,7 +14490,7 @@
         <v>23</v>
       </c>
       <c r="L187" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="M187" t="s">
         <v>23</v>
@@ -14528,10 +14519,10 @@
     </row>
     <row r="188" spans="1:20">
       <c r="A188" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B188" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="C188" t="s">
         <v>20</v>
@@ -14543,7 +14534,7 @@
         <v>38</v>
       </c>
       <c r="F188" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="G188" t="s">
         <v>23</v>
@@ -14561,7 +14552,7 @@
         <v>23</v>
       </c>
       <c r="L188" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="M188" t="s">
         <v>23</v>
@@ -14590,22 +14581,22 @@
     </row>
     <row r="189" spans="1:20">
       <c r="A189" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B189" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C189" t="s">
         <v>20</v>
       </c>
       <c r="D189" t="s">
-        <v>21</v>
+        <v>372</v>
       </c>
       <c r="E189" t="s">
-        <v>38</v>
+        <v>606</v>
       </c>
       <c r="F189" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="G189" t="s">
         <v>23</v>
@@ -14623,7 +14614,7 @@
         <v>23</v>
       </c>
       <c r="L189" t="s">
-        <v>759</v>
+        <v>23</v>
       </c>
       <c r="M189" t="s">
         <v>23</v>
@@ -14661,10 +14652,10 @@
         <v>20</v>
       </c>
       <c r="D190" t="s">
-        <v>375</v>
+        <v>21</v>
       </c>
       <c r="E190" t="s">
-        <v>609</v>
+        <v>22</v>
       </c>
       <c r="F190" t="s">
         <v>762</v>
@@ -14685,7 +14676,7 @@
         <v>23</v>
       </c>
       <c r="L190" t="s">
-        <v>23</v>
+        <v>763</v>
       </c>
       <c r="M190" t="s">
         <v>23</v>
@@ -14714,10 +14705,10 @@
     </row>
     <row r="191" spans="1:20">
       <c r="A191" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B191" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C191" t="s">
         <v>20</v>
@@ -14729,7 +14720,7 @@
         <v>22</v>
       </c>
       <c r="F191" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="G191" t="s">
         <v>23</v>
@@ -14747,7 +14738,7 @@
         <v>23</v>
       </c>
       <c r="L191" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="M191" t="s">
         <v>23</v>
@@ -14776,10 +14767,10 @@
     </row>
     <row r="192" spans="1:20">
       <c r="A192" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B192" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C192" t="s">
         <v>20</v>
@@ -14791,7 +14782,7 @@
         <v>22</v>
       </c>
       <c r="F192" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="G192" t="s">
         <v>23</v>
@@ -14809,7 +14800,7 @@
         <v>23</v>
       </c>
       <c r="L192" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="M192" t="s">
         <v>23</v>
@@ -14838,10 +14829,10 @@
     </row>
     <row r="193" spans="1:20">
       <c r="A193" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B193" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C193" t="s">
         <v>20</v>
@@ -14850,10 +14841,10 @@
         <v>21</v>
       </c>
       <c r="E193" t="s">
-        <v>22</v>
+        <v>399</v>
       </c>
       <c r="F193" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="G193" t="s">
         <v>23</v>
@@ -14871,7 +14862,7 @@
         <v>23</v>
       </c>
       <c r="L193" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="M193" t="s">
         <v>23</v>
@@ -14900,10 +14891,10 @@
     </row>
     <row r="194" spans="1:20">
       <c r="A194" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B194" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C194" t="s">
         <v>20</v>
@@ -14912,10 +14903,10 @@
         <v>21</v>
       </c>
       <c r="E194" t="s">
-        <v>402</v>
+        <v>431</v>
       </c>
       <c r="F194" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="G194" t="s">
         <v>23</v>
@@ -14933,7 +14924,7 @@
         <v>23</v>
       </c>
       <c r="L194" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="M194" t="s">
         <v>23</v>
@@ -14951,21 +14942,21 @@
         <v>23</v>
       </c>
       <c r="R194" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="S194">
         <v>0</v>
       </c>
       <c r="T194" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="195" spans="1:20">
       <c r="A195" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B195" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C195" t="s">
         <v>20</v>
@@ -14974,10 +14965,10 @@
         <v>21</v>
       </c>
       <c r="E195" t="s">
-        <v>434</v>
+        <v>399</v>
       </c>
       <c r="F195" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="G195" t="s">
         <v>23</v>
@@ -14995,7 +14986,7 @@
         <v>23</v>
       </c>
       <c r="L195" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="M195" t="s">
         <v>23</v>
@@ -15013,33 +15004,33 @@
         <v>23</v>
       </c>
       <c r="R195" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="S195">
         <v>0</v>
       </c>
       <c r="T195" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="196" spans="1:20">
       <c r="A196" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B196" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C196" t="s">
         <v>20</v>
       </c>
       <c r="D196" t="s">
-        <v>21</v>
+        <v>710</v>
       </c>
       <c r="E196" t="s">
-        <v>402</v>
+        <v>711</v>
       </c>
       <c r="F196" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="G196" t="s">
         <v>23</v>
@@ -15057,7 +15048,7 @@
         <v>23</v>
       </c>
       <c r="L196" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="M196" t="s">
         <v>23</v>
@@ -15086,22 +15077,22 @@
     </row>
     <row r="197" spans="1:20">
       <c r="A197" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B197" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C197" t="s">
         <v>20</v>
       </c>
       <c r="D197" t="s">
-        <v>713</v>
+        <v>21</v>
       </c>
       <c r="E197" t="s">
-        <v>714</v>
+        <v>38</v>
       </c>
       <c r="F197" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="G197" t="s">
         <v>23</v>
@@ -15119,7 +15110,7 @@
         <v>23</v>
       </c>
       <c r="L197" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="M197" t="s">
         <v>23</v>
@@ -15137,21 +15128,21 @@
         <v>23</v>
       </c>
       <c r="R197" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="S197">
         <v>0</v>
       </c>
       <c r="T197" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="198" spans="1:20">
       <c r="A198" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B198" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C198" t="s">
         <v>20</v>
@@ -15160,10 +15151,10 @@
         <v>21</v>
       </c>
       <c r="E198" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="F198" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="G198" t="s">
         <v>23</v>
@@ -15172,7 +15163,7 @@
         <v>23</v>
       </c>
       <c r="I198" t="s">
-        <v>23</v>
+        <v>795</v>
       </c>
       <c r="J198" t="s">
         <v>23</v>
@@ -15181,7 +15172,7 @@
         <v>23</v>
       </c>
       <c r="L198" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="M198" t="s">
         <v>23</v>
@@ -15199,21 +15190,21 @@
         <v>23</v>
       </c>
       <c r="R198" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="S198">
         <v>0</v>
       </c>
       <c r="T198" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="199" spans="1:20">
       <c r="A199" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="B199" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="C199" t="s">
         <v>20</v>
@@ -15222,10 +15213,10 @@
         <v>21</v>
       </c>
       <c r="E199" t="s">
-        <v>22</v>
+        <v>799</v>
       </c>
       <c r="F199" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="G199" t="s">
         <v>23</v>
@@ -15234,7 +15225,7 @@
         <v>23</v>
       </c>
       <c r="I199" t="s">
-        <v>798</v>
+        <v>23</v>
       </c>
       <c r="J199" t="s">
         <v>23</v>
@@ -15243,7 +15234,7 @@
         <v>23</v>
       </c>
       <c r="L199" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="M199" t="s">
         <v>23</v>
@@ -15261,95 +15252,69 @@
         <v>23</v>
       </c>
       <c r="R199" t="s">
-        <v>23</v>
+        <v>609</v>
       </c>
       <c r="S199">
         <v>0</v>
       </c>
       <c r="T199" t="s">
-        <v>23</v>
+        <v>610</v>
       </c>
     </row>
     <row r="200" spans="1:20">
-      <c r="A200" t="s">
-        <v>800</v>
-      </c>
-      <c r="B200" t="s">
-        <v>801</v>
-      </c>
-      <c r="C200" t="s">
-        <v>20</v>
-      </c>
-      <c r="D200" t="s">
+      <c r="A200" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="B200" s="3">
+        <v>49302206</v>
+      </c>
+      <c r="C200" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D200" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E200" t="s">
-        <v>802</v>
-      </c>
-      <c r="F200" t="s">
-        <v>803</v>
-      </c>
-      <c r="G200" t="s">
-        <v>23</v>
-      </c>
-      <c r="H200" t="s">
-        <v>23</v>
-      </c>
-      <c r="I200" t="s">
-        <v>23</v>
-      </c>
-      <c r="J200" t="s">
-        <v>23</v>
-      </c>
-      <c r="K200" t="s">
-        <v>23</v>
-      </c>
-      <c r="L200" t="s">
-        <v>804</v>
-      </c>
-      <c r="M200" t="s">
-        <v>23</v>
-      </c>
-      <c r="N200" t="s">
-        <v>23</v>
-      </c>
-      <c r="O200" t="s">
-        <v>23</v>
-      </c>
-      <c r="P200" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q200" t="s">
-        <v>23</v>
-      </c>
-      <c r="R200" t="s">
-        <v>612</v>
-      </c>
-      <c r="S200">
-        <v>0</v>
-      </c>
-      <c r="T200" t="s">
-        <v>613</v>
-      </c>
+      <c r="E200" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="F200" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="G200" s="2"/>
+      <c r="H200" s="2"/>
+      <c r="I200" s="2"/>
+      <c r="J200" s="2"/>
+      <c r="K200" s="2"/>
+      <c r="L200" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="M200" s="2"/>
+      <c r="N200" s="2"/>
+      <c r="O200" s="2"/>
+      <c r="P200" s="2"/>
+      <c r="Q200" s="2"/>
+      <c r="R200" s="2"/>
+      <c r="S200" s="2"/>
+      <c r="T200" s="2"/>
     </row>
     <row r="201" spans="1:20">
       <c r="A201" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="B201" s="3">
+        <v>11070834</v>
+      </c>
+      <c r="C201" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D201" s="2" t="s">
         <v>810</v>
       </c>
-      <c r="B201" s="3">
-        <v>49302206</v>
-      </c>
-      <c r="C201" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D201" s="2" t="s">
-        <v>21</v>
-      </c>
       <c r="E201" s="2" t="s">
-        <v>209</v>
+        <v>38</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="G201" s="2"/>
       <c r="H201" s="2"/>
@@ -15357,7 +15322,7 @@
       <c r="J201" s="2"/>
       <c r="K201" s="2"/>
       <c r="L201" s="2" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="M201" s="2"/>
       <c r="N201" s="2"/>
@@ -15370,19 +15335,19 @@
     </row>
     <row r="202" spans="1:20">
       <c r="A202" s="2" t="s">
-        <v>812</v>
-      </c>
-      <c r="B202" s="3">
-        <v>11070834</v>
+        <v>814</v>
+      </c>
+      <c r="B202" s="2">
+        <v>46490121</v>
       </c>
       <c r="C202" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>813</v>
+        <v>21</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>38</v>
+        <v>431</v>
       </c>
       <c r="F202" s="2" t="s">
         <v>815</v>
@@ -15406,22 +15371,22 @@
     </row>
     <row r="203" spans="1:20">
       <c r="A203" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="B203" s="2">
+        <v>26512390</v>
+      </c>
+      <c r="C203" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D203" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E203" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F203" s="2" t="s">
         <v>817</v>
-      </c>
-      <c r="B203" s="2">
-        <v>46490121</v>
-      </c>
-      <c r="C203" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D203" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E203" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="F203" s="2" t="s">
-        <v>818</v>
       </c>
       <c r="G203" s="2"/>
       <c r="H203" s="2"/>
@@ -15429,7 +15394,7 @@
       <c r="J203" s="2"/>
       <c r="K203" s="2"/>
       <c r="L203" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="M203" s="2"/>
       <c r="N203" s="2"/>
@@ -15442,26 +15407,28 @@
     </row>
     <row r="204" spans="1:20">
       <c r="A204" s="2" t="s">
-        <v>825</v>
+        <v>819</v>
       </c>
       <c r="B204" s="2">
-        <v>26512390</v>
+        <v>31443105</v>
       </c>
       <c r="C204" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>143</v>
+        <v>88</v>
       </c>
       <c r="F204" s="2" t="s">
         <v>820</v>
       </c>
       <c r="G204" s="2"/>
       <c r="H204" s="2"/>
-      <c r="I204" s="2"/>
+      <c r="I204" s="2">
+        <v>760863299</v>
+      </c>
       <c r="J204" s="2"/>
       <c r="K204" s="2"/>
       <c r="L204" s="2" t="s">
@@ -15478,10 +15445,10 @@
     </row>
     <row r="205" spans="1:20">
       <c r="A205" s="2" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B205" s="2">
-        <v>31443105</v>
+        <v>17237363</v>
       </c>
       <c r="C205" s="2" t="s">
         <v>20</v>
@@ -15490,20 +15457,18 @@
         <v>21</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>88</v>
+        <v>824</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="G205" s="2"/>
       <c r="H205" s="2"/>
-      <c r="I205" s="2">
-        <v>760863299</v>
-      </c>
+      <c r="I205" s="2"/>
       <c r="J205" s="2"/>
       <c r="K205" s="2"/>
       <c r="L205" s="2" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="M205" s="2"/>
       <c r="N205" s="2"/>
@@ -15514,23 +15479,23 @@
       <c r="S205" s="2"/>
       <c r="T205" s="2"/>
     </row>
-    <row r="206" spans="1:20">
-      <c r="A206" s="2" t="s">
-        <v>826</v>
-      </c>
-      <c r="B206" s="2">
-        <v>17237363</v>
+    <row r="206" spans="1:20" ht="17.25">
+      <c r="A206" s="4" t="s">
+        <v>830</v>
+      </c>
+      <c r="B206" s="4">
+        <v>47153060</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>20</v>
+        <v>827</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>827</v>
-      </c>
-      <c r="F206" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F206" s="5" t="s">
         <v>828</v>
       </c>
       <c r="G206" s="2"/>
@@ -15538,7 +15503,7 @@
       <c r="I206" s="2"/>
       <c r="J206" s="2"/>
       <c r="K206" s="2"/>
-      <c r="L206" s="2" t="s">
+      <c r="L206" s="6" t="s">
         <v>829</v>
       </c>
       <c r="M206" s="2"/>
@@ -15550,32 +15515,34 @@
       <c r="S206" s="2"/>
       <c r="T206" s="2"/>
     </row>
-    <row r="207" spans="1:20" ht="17.25">
-      <c r="A207" s="4" t="s">
-        <v>833</v>
-      </c>
-      <c r="B207" s="4">
-        <v>47153060</v>
+    <row r="207" spans="1:20">
+      <c r="A207" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="B207" s="2">
+        <v>15152880</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>830</v>
+        <v>20</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="F207" s="5" t="s">
-        <v>831</v>
+        <v>26</v>
+      </c>
+      <c r="F207" s="2" t="s">
+        <v>832</v>
       </c>
       <c r="G207" s="2"/>
       <c r="H207" s="2"/>
-      <c r="I207" s="2"/>
+      <c r="I207" s="7" t="s">
+        <v>834</v>
+      </c>
       <c r="J207" s="2"/>
       <c r="K207" s="2"/>
-      <c r="L207" s="6" t="s">
-        <v>832</v>
+      <c r="L207" s="2" t="s">
+        <v>833</v>
       </c>
       <c r="M207" s="2"/>
       <c r="N207" s="2"/>
@@ -15588,10 +15555,10 @@
     </row>
     <row r="208" spans="1:20">
       <c r="A208" s="2" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B208" s="2">
-        <v>15152880</v>
+        <v>14408671</v>
       </c>
       <c r="C208" s="2" t="s">
         <v>20</v>
@@ -15600,20 +15567,18 @@
         <v>21</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="G208" s="2"/>
       <c r="H208" s="2"/>
-      <c r="I208" s="7" t="s">
-        <v>837</v>
-      </c>
+      <c r="I208" s="2"/>
       <c r="J208" s="2"/>
       <c r="K208" s="2"/>
       <c r="L208" s="2" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="M208" s="2"/>
       <c r="N208" s="2"/>
@@ -15624,32 +15589,32 @@
       <c r="S208" s="2"/>
       <c r="T208" s="2"/>
     </row>
-    <row r="209" spans="1:20">
+    <row r="209" spans="1:20" ht="17.25">
       <c r="A209" s="2" t="s">
         <v>838</v>
       </c>
-      <c r="B209" s="2">
-        <v>14408671</v>
+      <c r="B209" s="4">
+        <v>42392937</v>
       </c>
       <c r="C209" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>22</v>
+        <v>148</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="G209" s="2"/>
       <c r="H209" s="2"/>
       <c r="I209" s="2"/>
       <c r="J209" s="2"/>
       <c r="K209" s="2"/>
-      <c r="L209" s="2" t="s">
-        <v>840</v>
+      <c r="L209" s="6" t="s">
+        <v>839</v>
       </c>
       <c r="M209" s="2"/>
       <c r="N209" s="2"/>
@@ -15661,20 +15626,20 @@
       <c r="T209" s="2"/>
     </row>
     <row r="210" spans="1:20" ht="17.25">
-      <c r="A210" s="2" t="s">
+      <c r="A210" s="8" t="s">
         <v>841</v>
       </c>
       <c r="B210" s="4">
-        <v>42392937</v>
+        <v>37004621</v>
       </c>
       <c r="C210" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>148</v>
+        <v>842</v>
       </c>
       <c r="F210" s="2" t="s">
         <v>843</v>
@@ -15684,8 +15649,8 @@
       <c r="I210" s="2"/>
       <c r="J210" s="2"/>
       <c r="K210" s="2"/>
-      <c r="L210" s="6" t="s">
-        <v>842</v>
+      <c r="L210" s="4" t="s">
+        <v>844</v>
       </c>
       <c r="M210" s="2"/>
       <c r="N210" s="2"/>
@@ -15696,12 +15661,12 @@
       <c r="S210" s="2"/>
       <c r="T210" s="2"/>
     </row>
-    <row r="211" spans="1:20" ht="17.25">
-      <c r="A211" s="8" t="s">
-        <v>844</v>
-      </c>
-      <c r="B211" s="4">
-        <v>37004621</v>
+    <row r="211" spans="1:20">
+      <c r="A211" s="2" t="s">
+        <v>845</v>
+      </c>
+      <c r="B211" s="2">
+        <v>24338654</v>
       </c>
       <c r="C211" s="2" t="s">
         <v>20</v>
@@ -15710,7 +15675,7 @@
         <v>21</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>845</v>
+        <v>38</v>
       </c>
       <c r="F211" s="2" t="s">
         <v>846</v>
@@ -15720,9 +15685,7 @@
       <c r="I211" s="2"/>
       <c r="J211" s="2"/>
       <c r="K211" s="2"/>
-      <c r="L211" s="4" t="s">
-        <v>847</v>
-      </c>
+      <c r="L211" s="2"/>
       <c r="M211" s="2"/>
       <c r="N211" s="2"/>
       <c r="O211" s="2"/>
@@ -15733,24 +15696,12 @@
       <c r="T211" s="2"/>
     </row>
     <row r="212" spans="1:20">
-      <c r="A212" s="2" t="s">
-        <v>848</v>
-      </c>
-      <c r="B212" s="2">
-        <v>24338654</v>
-      </c>
-      <c r="C212" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D212" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E212" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F212" s="2" t="s">
-        <v>849</v>
-      </c>
+      <c r="A212" s="2"/>
+      <c r="B212" s="2"/>
+      <c r="C212" s="2"/>
+      <c r="D212" s="2"/>
+      <c r="E212" s="2"/>
+      <c r="F212" s="2"/>
       <c r="G212" s="2"/>
       <c r="H212" s="2"/>
       <c r="I212" s="2"/>
@@ -15766,28 +15717,6 @@
       <c r="S212" s="2"/>
       <c r="T212" s="2"/>
     </row>
-    <row r="213" spans="1:20">
-      <c r="A213" s="2"/>
-      <c r="B213" s="2"/>
-      <c r="C213" s="2"/>
-      <c r="D213" s="2"/>
-      <c r="E213" s="2"/>
-      <c r="F213" s="2"/>
-      <c r="G213" s="2"/>
-      <c r="H213" s="2"/>
-      <c r="I213" s="2"/>
-      <c r="J213" s="2"/>
-      <c r="K213" s="2"/>
-      <c r="L213" s="2"/>
-      <c r="M213" s="2"/>
-      <c r="N213" s="2"/>
-      <c r="O213" s="2"/>
-      <c r="P213" s="2"/>
-      <c r="Q213" s="2"/>
-      <c r="R213" s="2"/>
-      <c r="S213" s="2"/>
-      <c r="T213" s="2"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/LISTA_CLIENTI.xlsx
+++ b/LISTA_CLIENTI.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3842" uniqueCount="847">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3848" uniqueCount="850">
   <si>
     <t>denumire</t>
   </si>
@@ -2555,6 +2555,15 @@
   </si>
   <si>
     <t>IOAN ALEXANDRU, NR37A, AP15</t>
+  </si>
+  <si>
+    <t>PASCA AUTO SRL</t>
+  </si>
+  <si>
+    <t>STR. 9 MAI, NR.71A</t>
+  </si>
+  <si>
+    <t>J2023001590208</t>
   </si>
 </sst>
 </file>
@@ -15695,19 +15704,33 @@
       <c r="S211" s="2"/>
       <c r="T211" s="2"/>
     </row>
-    <row r="212" spans="1:20">
-      <c r="A212" s="2"/>
-      <c r="B212" s="2"/>
-      <c r="C212" s="2"/>
-      <c r="D212" s="2"/>
-      <c r="E212" s="2"/>
-      <c r="F212" s="2"/>
+    <row r="212" spans="1:20" ht="17.25">
+      <c r="A212" s="4" t="s">
+        <v>847</v>
+      </c>
+      <c r="B212" s="4">
+        <v>49283430</v>
+      </c>
+      <c r="C212" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D212" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E212" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="F212" s="2" t="s">
+        <v>848</v>
+      </c>
       <c r="G212" s="2"/>
       <c r="H212" s="2"/>
       <c r="I212" s="2"/>
       <c r="J212" s="2"/>
       <c r="K212" s="2"/>
-      <c r="L212" s="2"/>
+      <c r="L212" s="4" t="s">
+        <v>849</v>
+      </c>
       <c r="M212" s="2"/>
       <c r="N212" s="2"/>
       <c r="O212" s="2"/>

--- a/LISTA_CLIENTI.xlsx
+++ b/LISTA_CLIENTI.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3848" uniqueCount="850">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3854" uniqueCount="853">
   <si>
     <t>denumire</t>
   </si>
@@ -2564,6 +2564,15 @@
   </si>
   <si>
     <t>J2023001590208</t>
+  </si>
+  <si>
+    <t>DANE TRANS COM SRL</t>
+  </si>
+  <si>
+    <t>CALEA MOTILOR 187</t>
+  </si>
+  <si>
+    <t>J1994001275013</t>
   </si>
 </sst>
 </file>
@@ -2643,8 +2652,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:T212" totalsRowShown="0">
-  <autoFilter ref="A1:T212"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:T214" totalsRowShown="0">
+  <autoFilter ref="A1:T214"/>
   <tableColumns count="20">
     <tableColumn id="1" name="denumire"/>
     <tableColumn id="2" name="cod_fiscal"/>
@@ -2956,7 +2965,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T212"/>
+  <dimension ref="A1:T214"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="45.85546875" customWidth="1"/>
@@ -15740,6 +15749,64 @@
       <c r="S212" s="2"/>
       <c r="T212" s="2"/>
     </row>
+    <row r="213" spans="1:20">
+      <c r="A213" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="B213">
+        <v>6615870</v>
+      </c>
+      <c r="C213" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D213" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="E213" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F213" s="2" t="s">
+        <v>851</v>
+      </c>
+      <c r="G213" s="2"/>
+      <c r="H213" s="2"/>
+      <c r="I213" s="2"/>
+      <c r="J213" s="2"/>
+      <c r="K213" s="2"/>
+      <c r="L213" t="s">
+        <v>852</v>
+      </c>
+      <c r="M213" s="2"/>
+      <c r="N213" s="2"/>
+      <c r="O213" s="2"/>
+      <c r="P213" s="2"/>
+      <c r="Q213" s="2"/>
+      <c r="R213" s="2"/>
+      <c r="S213" s="2"/>
+      <c r="T213" s="2"/>
+    </row>
+    <row r="214" spans="1:20">
+      <c r="A214" s="2"/>
+      <c r="B214" s="2"/>
+      <c r="C214" s="2"/>
+      <c r="D214" s="2"/>
+      <c r="E214" s="2"/>
+      <c r="F214" s="2"/>
+      <c r="G214" s="2"/>
+      <c r="H214" s="2"/>
+      <c r="I214" s="2"/>
+      <c r="J214" s="2"/>
+      <c r="K214" s="2"/>
+      <c r="L214" s="2"/>
+      <c r="M214" s="2"/>
+      <c r="N214" s="2"/>
+      <c r="O214" s="2"/>
+      <c r="P214" s="2"/>
+      <c r="Q214" s="2"/>
+      <c r="R214" s="2"/>
+      <c r="S214" s="2"/>
+      <c r="T214" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/LISTA_CLIENTI.xlsx
+++ b/LISTA_CLIENTI.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3854" uniqueCount="853">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3860" uniqueCount="856">
   <si>
     <t>denumire</t>
   </si>
@@ -2573,6 +2573,15 @@
   </si>
   <si>
     <t>J1994001275013</t>
+  </si>
+  <si>
+    <t>RAGOM SRL</t>
+  </si>
+  <si>
+    <t>Str.Costache Negruzzi 21</t>
+  </si>
+  <si>
+    <t>J2008000383019</t>
   </si>
 </sst>
 </file>
@@ -2652,8 +2661,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:T214" totalsRowShown="0">
-  <autoFilter ref="A1:T214"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:T215" totalsRowShown="0">
+  <autoFilter ref="A1:T215"/>
   <tableColumns count="20">
     <tableColumn id="1" name="denumire"/>
     <tableColumn id="2" name="cod_fiscal"/>
@@ -2965,7 +2974,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T214"/>
+  <dimension ref="A1:T215"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="45.85546875" customWidth="1"/>
@@ -15786,18 +15795,34 @@
       <c r="T213" s="2"/>
     </row>
     <row r="214" spans="1:20">
-      <c r="A214" s="2"/>
-      <c r="B214" s="2"/>
-      <c r="C214" s="2"/>
-      <c r="D214" s="2"/>
-      <c r="E214" s="2"/>
-      <c r="F214" s="2"/>
+      <c r="A214" s="2" t="s">
+        <v>853</v>
+      </c>
+      <c r="B214" s="2">
+        <v>23556316</v>
+      </c>
+      <c r="C214" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D214" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E214" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F214" s="2" t="s">
+        <v>854</v>
+      </c>
       <c r="G214" s="2"/>
       <c r="H214" s="2"/>
-      <c r="I214" s="2"/>
+      <c r="I214" s="2">
+        <v>727311764</v>
+      </c>
       <c r="J214" s="2"/>
       <c r="K214" s="2"/>
-      <c r="L214" s="2"/>
+      <c r="L214" s="2" t="s">
+        <v>855</v>
+      </c>
       <c r="M214" s="2"/>
       <c r="N214" s="2"/>
       <c r="O214" s="2"/>
@@ -15807,6 +15832,28 @@
       <c r="S214" s="2"/>
       <c r="T214" s="2"/>
     </row>
+    <row r="215" spans="1:20">
+      <c r="A215" s="2"/>
+      <c r="B215" s="2"/>
+      <c r="C215" s="2"/>
+      <c r="D215" s="2"/>
+      <c r="E215" s="2"/>
+      <c r="F215" s="2"/>
+      <c r="G215" s="2"/>
+      <c r="H215" s="2"/>
+      <c r="I215" s="2"/>
+      <c r="J215" s="2"/>
+      <c r="K215" s="2"/>
+      <c r="L215" s="2"/>
+      <c r="M215" s="2"/>
+      <c r="N215" s="2"/>
+      <c r="O215" s="2"/>
+      <c r="P215" s="2"/>
+      <c r="Q215" s="2"/>
+      <c r="R215" s="2"/>
+      <c r="S215" s="2"/>
+      <c r="T215" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
